--- a/장수/이름있는_장수_목록.xlsx
+++ b/장수/이름있는_장수_목록.xlsx
@@ -12,7 +12,7 @@
     <sheet name="병종으로 처리" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'이름있는 장수'!$A$4:$M$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'이름있는 장수'!$A$4:$O$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -106,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -125,6 +125,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -499,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -593,88 +596,105 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>고유특성을 구현한 장수(규칙판 8)</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>선정 기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>1. 사용자가 지정한 31명(사마의·조조·허저·하후돈·하후연·장료·서황·장합·조인·순욱·마초·유비·관우·장비·제갈량·조운·황충·강유·방통·주유·손권·육손·여몽·감녕·노숙·황개·위연·여포·진궁·유방·항우).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2. 『삼국지연의』에서 이름난 일화(별호·고사)가 있는 장수와 책사.</t>
+          <t>1. 사용자가 지정한 31명(사마의·조조·허저·하후돈·하후연·장료·서황·장합·조인·순욱·마초·유비·관우·장비·제갈량·조운·황충·강유·방통·주유·손권·육손·여몽·감녕·노숙·황개·위연·여포·진궁·유방·항우).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>3. 정사에 업적이 뚜렷하게 남은 인물(왕조 창업·대전투 지휘·국가 존망을 가른 인물).</t>
+          <t>2. 『삼국지연의』에서 이름난 일화(별호·고사)가 있는 장수와 책사.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>4. 게임에 이미 나오는 초한(楚漢) 영웅 중 고사가 뚜렷한 인물.</t>
+          <t>3. 정사에 업적이 뚜렷하게 남은 인물(왕조 창업·대전투 지휘·국가 존망을 가른 인물).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
+          <t>4. 게임에 이미 나오는 초한(楚漢) 영웅 중 고사가 뚜렷한 인물.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
           <t>5. 이 목록 밖의 인물은 이름을 달고 나와도 병종 능력만 쓴다(고유특성 없음).</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr"/>
-    </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>범례</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>· 초록 칸(구분=지정): 사용자가 직접 지정한 장수</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>· 노란 칸: 제안 고유특성·효과 초안(확정 전). 확정되면 게임에 하나씩 고유 효과로 구현한다.</t>
+          <t>· 초록 칸(구분=지정): 사용자가 직접 지정한 장수</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>· 주황 칸(현재 효과 종류): 지금 게임에서 3명 이상이 같은 효과를 공유하는 경우 — "장수 특성이 다 똑같다"의 원인.</t>
+          <t>· 노란 칸: 처음 제안한 초안. 초록 칸(구현된 고유특성): 실제 게임에 들어간 이름·효과(규칙판 8). 게임 엔진에 맞게 초안과 다르게 바꾼 것이 있다.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>· 숫자(요약·같은 효과 장수 수)는 파일 생성 시점에 계산해 넣은 값이다. 목록을 고치면 다시 세어야 한다.</t>
+          <t>· 게임에 없는 25명은 만들지 않았다. 목록 밖 게임 인물은 장수 특성 없이 병종 능력만 쓴다.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>· 주황 칸(현재 효과 종류): 지금 게임에서 3명 이상이 같은 효과를 공유하는 경우 — "장수 특성이 다 똑같다"의 원인.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>· 숫자(요약·같은 효과 장수 수)는 파일 생성 시점에 계산해 넣은 값이다. 목록을 고치면 다시 세어야 한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>· 현재 효과 종류 physicalPower = 물리 피해 증가, penetrate = 방어 관통, commandDefense = 통솔 방어 등. 출처: sama-game packages/web/src/romance.ts</t>
         </is>
@@ -691,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M99"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -707,6 +727,8 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="52" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -766,17 +788,17 @@
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>현재 고유능력</t>
+          <t>옛 고유능력(규칙판 7)</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>현재 효과 종류</t>
+          <t>옛 효과 종류</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>같은 효과를 쓰는 게임 인물 수</t>
+          <t>같은 효과를 쓰던 게임 인물 수</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
@@ -787,6 +809,16 @@
       <c r="M4" s="5" t="inlineStr">
         <is>
           <t>제안 효과(초안)</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>구현된 고유특성(규칙판 8)</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>구현 효과(1단계 · 4단계는 ×1.5)</t>
         </is>
       </c>
     </row>
@@ -846,6 +878,16 @@
           <t>받는 책략 피해 50% 감소, 사마의에게 책략을 쓴 적은 1턴 혼란</t>
         </is>
       </c>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>응시낭고</t>
+        </is>
+      </c>
+      <c r="O5" s="10" t="inlineStr">
+        <is>
+          <t>받는 책략 피해 25% 감소. 자기 차례마다 3칸 안 적 책사 하나의 책략을 봉인한다.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
@@ -903,6 +945,16 @@
           <t>아군이 적 장수를 퇴각시키면 조조 인접 아군 1명 재행동(턴당 1회)</t>
         </is>
       </c>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>난세의 간웅</t>
+        </is>
+      </c>
+      <c r="O6" s="10" t="inlineStr">
+        <is>
+          <t>이름있는 적 장수에게 주는 피해 20% 증가. 자기 차례마다 2칸 안 아군의 사기를 북돋운다(공격 +12%).</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
@@ -966,6 +1018,16 @@
           <t>체력 50% 이하일 때 무력 +30%, 받는 물리 피해 +10%</t>
         </is>
       </c>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>나의 결투</t>
+        </is>
+      </c>
+      <c r="O7" s="10" t="inlineStr">
+        <is>
+          <t>체력 절반 이하에서 물리 피해 30% 증가. 대신 받는 물리 피해 10% 증가.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
@@ -1011,7 +1073,7 @@
           <t>발시담정</t>
         </is>
       </c>
-      <c r="J8" s="10" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>veteran</t>
         </is>
@@ -1027,6 +1089,16 @@
       <c r="M8" s="9" t="inlineStr">
         <is>
           <t>처음으로 체력 30% 이하가 되면 체력 30% 회복, 2턴 동안 공격 +25%</t>
+        </is>
+      </c>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>발시담정</t>
+        </is>
+      </c>
+      <c r="O8" s="10" t="inlineStr">
+        <is>
+          <t>체력이 30% 이하로 떨어지면 자기 차례에 최대 체력의 25%를 회복한다(전투당 한 번).</t>
         </is>
       </c>
     </row>
@@ -1086,6 +1158,16 @@
           <t>이동력 +2, 이번 턴 이동한 칸 수 × 3% 공격 증가(최대 +24%)</t>
         </is>
       </c>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>전이병귀신속</t>
+        </is>
+      </c>
+      <c r="O9" s="10" t="inlineStr">
+        <is>
+          <t>이번 차례 움직인 칸마다 물리 피해 4% 증가(최대 6칸).</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
@@ -1131,7 +1213,7 @@
           <t>요래요래</t>
         </is>
       </c>
-      <c r="J10" s="10" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>penetrate</t>
         </is>
@@ -1147,6 +1229,16 @@
       <c r="M10" s="9" t="inlineStr">
         <is>
           <t>3칸 안의 적 공격 -15%, 장료가 먼저 친 적은 반격하지 못함</t>
+        </is>
+      </c>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>요래요래</t>
+        </is>
+      </c>
+      <c r="O10" s="10" t="inlineStr">
+        <is>
+          <t>체력이 가득한 적을 치면 피해 15% 증가, 반격을 받지 않는다.</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1286,7 @@
           <t>장구한 포위</t>
         </is>
       </c>
-      <c r="J11" s="10" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr">
         <is>
           <t>penetrate</t>
         </is>
@@ -1210,6 +1302,16 @@
       <c r="M11" s="9" t="inlineStr">
         <is>
           <t>아군 2명 이상에 둘러싸인 적에게 주는 피해 +30%</t>
+        </is>
+      </c>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>장구한 포위</t>
+        </is>
+      </c>
+      <c r="O11" s="10" t="inlineStr">
+        <is>
+          <t>대상 곁에 다른 아군이 둘 이상 붙어 있으면 피해 25% 증가.</t>
         </is>
       </c>
     </row>
@@ -1275,6 +1377,16 @@
           <t>지형 불리 무시, 반격을 먼저 친다(선제 반격)</t>
         </is>
       </c>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>교변</t>
+        </is>
+      </c>
+      <c r="O12" s="10" t="inlineStr">
+        <is>
+          <t>험한 지형도 평지처럼 움직인다. 두 칸 이상 떨어진 적에게 받는 피해 20% 감소.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
@@ -1320,7 +1432,7 @@
           <t>철벽 수성</t>
         </is>
       </c>
-      <c r="J13" s="10" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr">
         <is>
           <t>commandDefense</t>
         </is>
@@ -1336,6 +1448,16 @@
       <c r="M13" s="9" t="inlineStr">
         <is>
           <t>성채·성문·요새 칸에서 받는 피해 -40%, 인접 아군 방어 +15%</t>
+        </is>
+      </c>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>철벽 수성</t>
+        </is>
+      </c>
+      <c r="O13" s="10" t="inlineStr">
+        <is>
+          <t>성채·성문 칸에서 받는 피해 30% 감소, 그 밖에서는 8% 감소.</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1505,7 @@
           <t>왕좌지재</t>
         </is>
       </c>
-      <c r="J14" s="10" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr">
         <is>
           <t>strategicGuard</t>
         </is>
@@ -1399,6 +1521,16 @@
       <c r="M14" s="9" t="inlineStr">
         <is>
           <t>전장의 아군 책사 전원 매 턴 MP +5</t>
+        </is>
+      </c>
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t>왕좌지재</t>
+        </is>
+      </c>
+      <c r="O14" s="10" t="inlineStr">
+        <is>
+          <t>자기 차례마다 전장의 아군 책사 모두의 책략 기력(MP)을 4 채운다.</t>
         </is>
       </c>
     </row>
@@ -1464,6 +1596,16 @@
           <t>기병일 때 돌진한 칸마다 피해 +8%(최대 +40%), 조씨 장수에게 +20%</t>
         </is>
       </c>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>금마초</t>
+        </is>
+      </c>
+      <c r="O15" s="10" t="inlineStr">
+        <is>
+          <t>움직인 뒤 공격하면 피해 15% 증가. 조씨 장수에게는 15% 더.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
@@ -1509,7 +1651,7 @@
           <t>인덕</t>
         </is>
       </c>
-      <c r="J16" s="10" t="inlineStr">
+      <c r="J16" s="11" t="inlineStr">
         <is>
           <t>commandDefense</t>
         </is>
@@ -1525,6 +1667,16 @@
       <c r="M16" s="9" t="inlineStr">
         <is>
           <t>인접 아군 매 턴 체력 10% 회복, 유비가 퇴각하면 아군 전원 공격 +20%</t>
+        </is>
+      </c>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>인덕</t>
+        </is>
+      </c>
+      <c r="O16" s="10" t="inlineStr">
+        <is>
+          <t>자기 차례마다 곁에 붙은 아군의 체력을 8% 회복한다.</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1724,7 @@
           <t>청룡언월도</t>
         </is>
       </c>
-      <c r="J17" s="10" t="inlineStr">
+      <c r="J17" s="11" t="inlineStr">
         <is>
           <t>physicalPower</t>
         </is>
@@ -1588,6 +1740,16 @@
       <c r="M17" s="9" t="inlineStr">
         <is>
           <t>적 장수 공격 시 피해 +20%, 첫 공격 회심 확률 +30%</t>
+        </is>
+      </c>
+      <c r="N17" s="10" t="inlineStr">
+        <is>
+          <t>무성</t>
+        </is>
+      </c>
+      <c r="O17" s="10" t="inlineStr">
+        <is>
+          <t>이름있는 적 장수를 물리 공격하면 피해 20% 증가, 회심 확률 +10%p.</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1797,7 @@
           <t>장판교의 일갈</t>
         </is>
       </c>
-      <c r="J18" s="10" t="inlineStr">
+      <c r="J18" s="11" t="inlineStr">
         <is>
           <t>physicalPower</t>
         </is>
@@ -1651,6 +1813,16 @@
       <c r="M18" s="9" t="inlineStr">
         <is>
           <t>턴당 1회, 3칸 안 적 전원 1턴 이동 불가(위협)</t>
+        </is>
+      </c>
+      <c r="N18" s="10" t="inlineStr">
+        <is>
+          <t>장판교의 일갈</t>
+        </is>
+      </c>
+      <c r="O18" s="10" t="inlineStr">
+        <is>
+          <t>자기 차례마다 2칸 안 적 모두를 쇠약하게 한다(공격 15% 감소).</t>
         </is>
       </c>
     </row>
@@ -1716,6 +1888,16 @@
           <t>바람·불 책략 위력 +30%, 3×3 팔진을 쳐 들어온 적 혼란</t>
         </is>
       </c>
+      <c r="N19" s="10" t="inlineStr">
+        <is>
+          <t>와룡</t>
+        </is>
+      </c>
+      <c r="O19" s="10" t="inlineStr">
+        <is>
+          <t>불·바람 책략 피해 25% 증가. 받는 책략 피해 15% 감소.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
@@ -1761,7 +1943,7 @@
           <t>단기필마</t>
         </is>
       </c>
-      <c r="J20" s="10" t="inlineStr">
+      <c r="J20" s="11" t="inlineStr">
         <is>
           <t>veteran</t>
         </is>
@@ -1777,6 +1959,16 @@
       <c r="M20" s="9" t="inlineStr">
         <is>
           <t>인접 적 3 이상일 때 받는 피해 -30%, 적 사이를 지나 이동 가능</t>
+        </is>
+      </c>
+      <c r="N20" s="10" t="inlineStr">
+        <is>
+          <t>단기필마</t>
+        </is>
+      </c>
+      <c r="O20" s="10" t="inlineStr">
+        <is>
+          <t>곁에 붙은 적이 둘 이상이면 받는 피해 25% 감소, 주는 피해 10% 증가.</t>
         </is>
       </c>
     </row>
@@ -1824,7 +2016,7 @@
           <t>노익장</t>
         </is>
       </c>
-      <c r="J21" s="10" t="inlineStr">
+      <c r="J21" s="11" t="inlineStr">
         <is>
           <t>penetrate</t>
         </is>
@@ -1840,6 +2032,16 @@
       <c r="M21" s="9" t="inlineStr">
         <is>
           <t>원거리 사거리 +1, 체력이 가득할 때 주는 피해 +25%</t>
+        </is>
+      </c>
+      <c r="N21" s="10" t="inlineStr">
+        <is>
+          <t>노익장</t>
+        </is>
+      </c>
+      <c r="O21" s="10" t="inlineStr">
+        <is>
+          <t>두 칸 이상 떨어진 적에게 물리 피해 15% 증가. 체력이 가득하면 회심 확률 +15%p.</t>
         </is>
       </c>
     </row>
@@ -1887,7 +2089,7 @@
           <t>기린아</t>
         </is>
       </c>
-      <c r="J22" s="10" t="inlineStr">
+      <c r="J22" s="11" t="inlineStr">
         <is>
           <t>physicalPower</t>
         </is>
@@ -1903,6 +2105,16 @@
       <c r="M22" s="9" t="inlineStr">
         <is>
           <t>일기토·설전 모두 가능, 무력·지력 중 높은 쪽으로 공격·책략</t>
+        </is>
+      </c>
+      <c r="N22" s="10" t="inlineStr">
+        <is>
+          <t>기린아</t>
+        </is>
+      </c>
+      <c r="O22" s="10" t="inlineStr">
+        <is>
+          <t>물리 공격에 지력의 15%만큼 피해를 더한다. 책략 명중 +10%p.</t>
         </is>
       </c>
     </row>
@@ -1950,7 +2162,7 @@
           <t>연환계</t>
         </is>
       </c>
-      <c r="J23" s="10" t="inlineStr">
+      <c r="J23" s="11" t="inlineStr">
         <is>
           <t>strategyPower</t>
         </is>
@@ -1966,6 +2178,16 @@
       <c r="M23" s="9" t="inlineStr">
         <is>
           <t>책략 피해가 인접한 적에게 50%씩 이어진다</t>
+        </is>
+      </c>
+      <c r="N23" s="10" t="inlineStr">
+        <is>
+          <t>연환계</t>
+        </is>
+      </c>
+      <c r="O23" s="10" t="inlineStr">
+        <is>
+          <t>책략 대상 곁에 붙은 다른 적 하나마다 책략 피해 8% 증가(최대 4).</t>
         </is>
       </c>
     </row>
@@ -2031,6 +2253,16 @@
           <t>화계 범위 +1, 물·수상의 적에게 화계 피해 +50%</t>
         </is>
       </c>
+      <c r="N24" s="10" t="inlineStr">
+        <is>
+          <t>적벽의 화공</t>
+        </is>
+      </c>
+      <c r="O24" s="10" t="inlineStr">
+        <is>
+          <t>불 책략 피해 20% 증가. 물 위나 물가의 적에게는 30% 더.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
@@ -2076,7 +2308,7 @@
           <t>강동 수성</t>
         </is>
       </c>
-      <c r="J25" s="10" t="inlineStr">
+      <c r="J25" s="11" t="inlineStr">
         <is>
           <t>commandDefense</t>
         </is>
@@ -2092,6 +2324,16 @@
       <c r="M25" s="9" t="inlineStr">
         <is>
           <t>손권이 살아 있으면 아군 전원 방어 +10%, 매 턴 MP +3</t>
+        </is>
+      </c>
+      <c r="N25" s="10" t="inlineStr">
+        <is>
+          <t>벽안자염</t>
+        </is>
+      </c>
+      <c r="O25" s="10" t="inlineStr">
+        <is>
+          <t>3칸 안 아군 하나마다 받는 피해 5% 감소(최대 4). 자기 차례마다 MP 3 회복.</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2381,7 @@
           <t>이릉의 화공</t>
         </is>
       </c>
-      <c r="J26" s="10" t="inlineStr">
+      <c r="J26" s="11" t="inlineStr">
         <is>
           <t>strategyPower</t>
         </is>
@@ -2155,6 +2397,16 @@
       <c r="M26" s="9" t="inlineStr">
         <is>
           <t>숲·풀 위의 적에게 화계 위력 2배, 불 지속 +1턴</t>
+        </is>
+      </c>
+      <c r="N26" s="10" t="inlineStr">
+        <is>
+          <t>이릉의 화공</t>
+        </is>
+      </c>
+      <c r="O26" s="10" t="inlineStr">
+        <is>
+          <t>숲·갈대늪 위의 적에게 불 책략 피해 40% 증가.</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2454,7 @@
           <t>백의도강</t>
         </is>
       </c>
-      <c r="J27" s="10" t="inlineStr">
+      <c r="J27" s="11" t="inlineStr">
         <is>
           <t>penetrate</t>
         </is>
@@ -2218,6 +2470,16 @@
       <c r="M27" s="9" t="inlineStr">
         <is>
           <t>전투 첫 2턴 적 시야에 보이지 않음, 숨은 채 첫 공격 피해 +50%</t>
+        </is>
+      </c>
+      <c r="N27" s="10" t="inlineStr">
+        <is>
+          <t>백의도강</t>
+        </is>
+      </c>
+      <c r="O27" s="10" t="inlineStr">
+        <is>
+          <t>전투 첫 두 턴 동안 주는 피해 25% 증가, 방어 15% 무시.</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2527,7 @@
           <t>백기 야습</t>
         </is>
       </c>
-      <c r="J28" s="10" t="inlineStr">
+      <c r="J28" s="11" t="inlineStr">
         <is>
           <t>physicalPower</t>
         </is>
@@ -2281,6 +2543,16 @@
       <c r="M28" s="9" t="inlineStr">
         <is>
           <t>적 3명 이상 인접 시 회피 +20%, 적 진영 깊이 들어갈수록 공격 +10%</t>
+        </is>
+      </c>
+      <c r="N28" s="10" t="inlineStr">
+        <is>
+          <t>백기겁영</t>
+        </is>
+      </c>
+      <c r="O28" s="10" t="inlineStr">
+        <is>
+          <t>곁에 붙은 적 하나마다 회피 +8%p, 주는 피해 6% 증가(최대 3).</t>
         </is>
       </c>
     </row>
@@ -2340,6 +2612,16 @@
           <t>우군(AI) 공격 +15%, 매 턴 적 1부대 공격 -10%(사기 저하)</t>
         </is>
       </c>
+      <c r="N29" s="10" t="inlineStr">
+        <is>
+          <t>손유 동맹</t>
+        </is>
+      </c>
+      <c r="O29" s="10" t="inlineStr">
+        <is>
+          <t>전장의 우군(동맹 부대)이 주는 피해 15% 증가.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
@@ -2397,6 +2679,16 @@
           <t>체력 20%를 써서 다음 화계 위력 2배·반드시 명중</t>
         </is>
       </c>
+      <c r="N30" s="10" t="inlineStr">
+        <is>
+          <t>고육계</t>
+        </is>
+      </c>
+      <c r="O30" s="10" t="inlineStr">
+        <is>
+          <t>자기 차례마다 체력 5%를 잃고, 그 차례 동안 사기가 오른다. 체력이 낮을수록 피해 증가(최대 30%).</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
@@ -2442,7 +2734,7 @@
           <t>반골의 용맹</t>
         </is>
       </c>
-      <c r="J31" s="10" t="inlineStr">
+      <c r="J31" s="11" t="inlineStr">
         <is>
           <t>physicalPower</t>
         </is>
@@ -2458,6 +2750,16 @@
       <c r="M31" s="9" t="inlineStr">
         <is>
           <t>인접 아군이 없을 때 공격 +25%</t>
+        </is>
+      </c>
+      <c r="N31" s="10" t="inlineStr">
+        <is>
+          <t>반골</t>
+        </is>
+      </c>
+      <c r="O31" s="10" t="inlineStr">
+        <is>
+          <t>곁에 붙은 아군이 없으면 주는 피해 25% 증가.</t>
         </is>
       </c>
     </row>
@@ -2523,6 +2825,16 @@
           <t>매 공격 2회 연속, 반격 피해 +30%</t>
         </is>
       </c>
+      <c r="N32" s="10" t="inlineStr">
+        <is>
+          <t>인중여포</t>
+        </is>
+      </c>
+      <c r="O32" s="10" t="inlineStr">
+        <is>
+          <t>물리 피해 15% 증가, 회심 확률 +15%p. 대신 받는 책략 피해 10% 증가.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
@@ -2568,7 +2880,7 @@
           <t>냉철한 간파</t>
         </is>
       </c>
-      <c r="J33" s="10" t="inlineStr">
+      <c r="J33" s="11" t="inlineStr">
         <is>
           <t>strategicGuard</t>
         </is>
@@ -2584,6 +2896,16 @@
       <c r="M33" s="9" t="inlineStr">
         <is>
           <t>받는 책략 회피 +30%, 매복·함정 칸 자동 발견</t>
+        </is>
+      </c>
+      <c r="N33" s="10" t="inlineStr">
+        <is>
+          <t>냉철한 간파</t>
+        </is>
+      </c>
+      <c r="O33" s="10" t="inlineStr">
+        <is>
+          <t>책략 회피 +20%p. 자기 차례마다 자신의 혼란·봉인을 푼다.</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2953,7 @@
           <t>관인대도</t>
         </is>
       </c>
-      <c r="J34" s="10" t="inlineStr">
+      <c r="J34" s="11" t="inlineStr">
         <is>
           <t>commandDefense</t>
         </is>
@@ -2647,6 +2969,16 @@
       <c r="M34" s="9" t="inlineStr">
         <is>
           <t>아군 장수 수 × 3 통솔 증가, 퇴각한 아군 1명 다음 턴 체력 30%로 복귀(1회)</t>
+        </is>
+      </c>
+      <c r="N34" s="10" t="inlineStr">
+        <is>
+          <t>관인대도</t>
+        </is>
+      </c>
+      <c r="O34" s="10" t="inlineStr">
+        <is>
+          <t>자기 차례마다 전장의 아군 모두의 체력을 3% 회복한다.</t>
         </is>
       </c>
     </row>
@@ -2694,7 +3026,7 @@
           <t>역발산</t>
         </is>
       </c>
-      <c r="J35" s="10" t="inlineStr">
+      <c r="J35" s="11" t="inlineStr">
         <is>
           <t>physicalPower</t>
         </is>
@@ -2710,6 +3042,16 @@
       <c r="M35" s="9" t="inlineStr">
         <is>
           <t>공격 대상과 인접한 적 전원에게 50% 피해, 체력 30% 이하일 때 공격 +30%(사면초가)</t>
+        </is>
+      </c>
+      <c r="N35" s="10" t="inlineStr">
+        <is>
+          <t>역발산기개세</t>
+        </is>
+      </c>
+      <c r="O35" s="10" t="inlineStr">
+        <is>
+          <t>물리 피해 20% 증가. 체력 30% 이하(사면초가)에서는 30% 더.</t>
         </is>
       </c>
     </row>
@@ -2767,6 +3109,16 @@
       <c r="M36" s="9" t="inlineStr">
         <is>
           <t>설전에서 상대 지력 -15%</t>
+        </is>
+      </c>
+      <c r="N36" s="10" t="inlineStr">
+        <is>
+          <t>칠보시</t>
+        </is>
+      </c>
+      <c r="O36" s="10" t="inlineStr">
+        <is>
+          <t>책략을 쓰는 적에게 주는 피해 20% 증가.</t>
         </is>
       </c>
     </row>
@@ -2818,6 +3170,12 @@
           <t>전투 시작 시 적 매복 위치 공개, 아군 책사 회피 +15%</t>
         </is>
       </c>
+      <c r="N37" s="8" t="inlineStr">
+        <is>
+          <t>게임에 없음 — 만들지 않음</t>
+        </is>
+      </c>
+      <c r="O37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
@@ -2863,7 +3221,7 @@
           <t>난무</t>
         </is>
       </c>
-      <c r="J38" s="10" t="inlineStr">
+      <c r="J38" s="11" t="inlineStr">
         <is>
           <t>strategyPower</t>
         </is>
@@ -2879,6 +3237,16 @@
       <c r="M38" s="9" t="inlineStr">
         <is>
           <t>책략 명중 시 30% 확률로 적 혼란</t>
+        </is>
+      </c>
+      <c r="N38" s="10" t="inlineStr">
+        <is>
+          <t>난무</t>
+        </is>
+      </c>
+      <c r="O38" s="10" t="inlineStr">
+        <is>
+          <t>혼란·봉인·쇠약·둔화에 걸린 적에게 주는 피해 30% 증가.</t>
         </is>
       </c>
     </row>
@@ -2930,6 +3298,12 @@
           <t>매 3턴마다 책략 MP 소모 0</t>
         </is>
       </c>
+      <c r="N39" s="8" t="inlineStr">
+        <is>
+          <t>게임에 없음 — 만들지 않음</t>
+        </is>
+      </c>
+      <c r="O39" s="8" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
@@ -2979,6 +3353,12 @@
           <t>적 책사 MP 매 턴 -3</t>
         </is>
       </c>
+      <c r="N40" s="8" t="inlineStr">
+        <is>
+          <t>게임에 없음 — 만들지 않음</t>
+        </is>
+      </c>
+      <c r="O40" s="8" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
@@ -3024,6 +3404,12 @@
           <t>인접 아군 대신 공격을 받음, 받는 피해 -20%</t>
         </is>
       </c>
+      <c r="N41" s="8" t="inlineStr">
+        <is>
+          <t>게임에 없음 — 만들지 않음</t>
+        </is>
+      </c>
+      <c r="O41" s="8" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
@@ -3073,6 +3459,12 @@
           <t>퇴각할 때까지 공격 +20%, 후퇴 불가</t>
         </is>
       </c>
+      <c r="N42" s="8" t="inlineStr">
+        <is>
+          <t>게임에 없음 — 만들지 않음</t>
+        </is>
+      </c>
+      <c r="O42" s="8" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
@@ -3130,6 +3522,16 @@
           <t>인접 아군 혼란·위협 무효</t>
         </is>
       </c>
+      <c r="N43" s="10" t="inlineStr">
+        <is>
+          <t>엄정한 군율</t>
+        </is>
+      </c>
+      <c r="O43" s="10" t="inlineStr">
+        <is>
+          <t>자기 차례마다 자신과 2칸 안 아군의 혼란·쇠약·둔화를 풀어 준다. 받는 피해 5% 감소.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
@@ -3185,6 +3587,16 @@
       <c r="M44" s="9" t="inlineStr">
         <is>
           <t>전투 첫 턴 이동력 +3, 첫 공격 피해 +20%</t>
+        </is>
+      </c>
+      <c r="N44" s="10" t="inlineStr">
+        <is>
+          <t>선봉</t>
+        </is>
+      </c>
+      <c r="O44" s="10" t="inlineStr">
+        <is>
+          <t>첫 턴에 이동력 +2. 자신의 체력이 가득할 때 물리 피해 20% 증가.</t>
         </is>
       </c>
     </row>
@@ -3236,6 +3648,12 @@
           <t>방어 태세 시 인접 아군 방어 +10%</t>
         </is>
       </c>
+      <c r="N45" s="8" t="inlineStr">
+        <is>
+          <t>게임에 없음 — 만들지 않음</t>
+        </is>
+      </c>
+      <c r="O45" s="8" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
@@ -3281,7 +3699,7 @@
           <t>음평 기습</t>
         </is>
       </c>
-      <c r="J46" s="10" t="inlineStr">
+      <c r="J46" s="11" t="inlineStr">
         <is>
           <t>penetrate</t>
         </is>
@@ -3297,6 +3715,16 @@
       <c r="M46" s="9" t="inlineStr">
         <is>
           <t>산지·절벽 옆 이동 비용 1, 산에서 내려온 첫 공격 +30%</t>
+        </is>
+      </c>
+      <c r="N46" s="10" t="inlineStr">
+        <is>
+          <t>음평 기습</t>
+        </is>
+      </c>
+      <c r="O46" s="10" t="inlineStr">
+        <is>
+          <t>산지·구릉에 서서 공격하면 피해 25% 증가.</t>
         </is>
       </c>
     </row>
@@ -3344,7 +3772,7 @@
           <t>사본론</t>
         </is>
       </c>
-      <c r="J47" s="10" t="inlineStr">
+      <c r="J47" s="11" t="inlineStr">
         <is>
           <t>strategyPower</t>
         </is>
@@ -3360,6 +3788,16 @@
       <c r="M47" s="9" t="inlineStr">
         <is>
           <t>책략 피해 +15%, 설전 승리 시 상대 진영 사기 저하</t>
+        </is>
+      </c>
+      <c r="N47" s="10" t="inlineStr">
+        <is>
+          <t>사본론</t>
+        </is>
+      </c>
+      <c r="O47" s="10" t="inlineStr">
+        <is>
+          <t>상대보다 지력이 높으면 그 차이만큼 책략 피해 증가(최대 25%).</t>
         </is>
       </c>
     </row>
@@ -3419,6 +3857,16 @@
           <t>적 기병의 돌진 피해 -30%</t>
         </is>
       </c>
+      <c r="N48" s="10" t="inlineStr">
+        <is>
+          <t>옹주 수비</t>
+        </is>
+      </c>
+      <c r="O48" s="10" t="inlineStr">
+        <is>
+          <t>기병에게 받는 피해 30% 감소.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
@@ -3464,7 +3912,7 @@
           <t>진창 수성</t>
         </is>
       </c>
-      <c r="J49" s="10" t="inlineStr">
+      <c r="J49" s="11" t="inlineStr">
         <is>
           <t>commandDefense</t>
         </is>
@@ -3480,6 +3928,16 @@
       <c r="M49" s="9" t="inlineStr">
         <is>
           <t>성 칸에서 반격 확정, 받는 공성 피해 -50%</t>
+        </is>
+      </c>
+      <c r="N49" s="10" t="inlineStr">
+        <is>
+          <t>진창 수성</t>
+        </is>
+      </c>
+      <c r="O49" s="10" t="inlineStr">
+        <is>
+          <t>성채·성문 칸에서 받은 물리 피해의 25%를 공격자에게 되돌린다.</t>
         </is>
       </c>
     </row>
@@ -3539,6 +3997,16 @@
           <t>체력 50% 이하에서도 능력 감소 없음, 반격 +15%</t>
         </is>
       </c>
+      <c r="N50" s="10" t="inlineStr">
+        <is>
+          <t>침착한 장자</t>
+        </is>
+      </c>
+      <c r="O50" s="10" t="inlineStr">
+        <is>
+          <t>사마의가 2칸 안에 있으면 주는 피해 15% 증가, 받는 피해 15% 감소.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
@@ -3596,6 +4064,16 @@
           <t>적 장수 퇴각 시 전 아군 MP +5</t>
         </is>
       </c>
+      <c r="N51" s="10" t="inlineStr">
+        <is>
+          <t>사마소의 마음</t>
+        </is>
+      </c>
+      <c r="O51" s="10" t="inlineStr">
+        <is>
+          <t>체력이 절반 이하인 적에게 주는 피해 20% 증가.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
@@ -3653,6 +4131,16 @@
           <t>인접 기병 공격 +10%</t>
         </is>
       </c>
+      <c r="N52" s="10" t="inlineStr">
+        <is>
+          <t>종실의 대들보</t>
+        </is>
+      </c>
+      <c r="O52" s="10" t="inlineStr">
+        <is>
+          <t>2칸 안 아군 기병의 물리 피해 12% 증가.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
@@ -3710,6 +4198,16 @@
           <t>인접 아군이 퇴각할 공격을 1회 대신 받음</t>
         </is>
       </c>
+      <c r="N53" s="10" t="inlineStr">
+        <is>
+          <t>헌마</t>
+        </is>
+      </c>
+      <c r="O53" s="10" t="inlineStr">
+        <is>
+          <t>곁에 붙은 아군이 받는 피해 10% 감소.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
@@ -3755,7 +4253,7 @@
           <t>황수아</t>
         </is>
       </c>
-      <c r="J54" s="10" t="inlineStr">
+      <c r="J54" s="11" t="inlineStr">
         <is>
           <t>physicalPower</t>
         </is>
@@ -3771,6 +4269,16 @@
       <c r="M54" s="9" t="inlineStr">
         <is>
           <t>이민족(오환·선비) 상대 피해 +25%</t>
+        </is>
+      </c>
+      <c r="N54" s="10" t="inlineStr">
+        <is>
+          <t>황수아</t>
+        </is>
+      </c>
+      <c r="O54" s="10" t="inlineStr">
+        <is>
+          <t>회심 확률 +10%p. 기병을 치면 피해 15% 증가.</t>
         </is>
       </c>
     </row>
@@ -3828,6 +4336,16 @@
       <c r="M55" s="9" t="inlineStr">
         <is>
           <t>물가 칸에서 방어 +20%</t>
+        </is>
+      </c>
+      <c r="N55" s="10" t="inlineStr">
+        <is>
+          <t>강하 수비</t>
+        </is>
+      </c>
+      <c r="O55" s="10" t="inlineStr">
+        <is>
+          <t>물가(물 칸 위나 옆)에서 받는 피해 20% 감소.</t>
         </is>
       </c>
     </row>
@@ -3879,6 +4397,12 @@
           <t>고지에 있는 아군 책략 위력 +20%</t>
         </is>
       </c>
+      <c r="N56" s="8" t="inlineStr">
+        <is>
+          <t>게임에 없음 — 만들지 않음</t>
+        </is>
+      </c>
+      <c r="O56" s="8" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
@@ -3928,6 +4452,12 @@
           <t>설득·설전 성공률 +20%</t>
         </is>
       </c>
+      <c r="N57" s="8" t="inlineStr">
+        <is>
+          <t>게임에 없음 — 만들지 않음</t>
+        </is>
+      </c>
+      <c r="O57" s="8" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
@@ -3985,6 +4515,16 @@
           <t>산·언덕에서 책략 +20%, 물 보급이 끊기면 -20%</t>
         </is>
       </c>
+      <c r="N58" s="10" t="inlineStr">
+        <is>
+          <t>가정의 고지</t>
+        </is>
+      </c>
+      <c r="O58" s="10" t="inlineStr">
+        <is>
+          <t>산지·구릉에서 책략 피해 20% 증가. 평지에서 받는 피해 10% 증가.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
@@ -4042,6 +4582,16 @@
           <t>요새·관문 칸에서 받는 피해 -25%</t>
         </is>
       </c>
+      <c r="N59" s="10" t="inlineStr">
+        <is>
+          <t>흥세 수비</t>
+        </is>
+      </c>
+      <c r="O59" s="10" t="inlineStr">
+        <is>
+          <t>길·다리·잔도 위에서 받는 피해 25% 감소.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
@@ -4093,6 +4643,16 @@
       <c r="M60" s="9" t="inlineStr">
         <is>
           <t>관우 인접 시 공격·방어 +15%</t>
+        </is>
+      </c>
+      <c r="N60" s="10" t="inlineStr">
+        <is>
+          <t>부자 동행</t>
+        </is>
+      </c>
+      <c r="O60" s="10" t="inlineStr">
+        <is>
+          <t>관우가 2칸 안에 있으면 주는 피해 15% 증가, 받는 피해 15% 감소.</t>
         </is>
       </c>
     </row>
@@ -4144,6 +4704,12 @@
           <t>적 장수 공격 시 피해 +15%</t>
         </is>
       </c>
+      <c r="N61" s="8" t="inlineStr">
+        <is>
+          <t>게임에 없음 — 만들지 않음</t>
+        </is>
+      </c>
+      <c r="O61" s="8" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
@@ -4189,6 +4755,12 @@
           <t>공격 범위 +1(창)</t>
         </is>
       </c>
+      <c r="N62" s="8" t="inlineStr">
+        <is>
+          <t>게임에 없음 — 만들지 않음</t>
+        </is>
+      </c>
+      <c r="O62" s="8" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
@@ -4234,6 +4806,12 @@
           <t>체력 70% 이상일 때 방어 +20%</t>
         </is>
       </c>
+      <c r="N63" s="8" t="inlineStr">
+        <is>
+          <t>게임에 없음 — 만들지 않음</t>
+        </is>
+      </c>
+      <c r="O63" s="8" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
@@ -4287,6 +4865,16 @@
           <t>배신·반골 특성 적에게 피해 +30%</t>
         </is>
       </c>
+      <c r="N64" s="10" t="inlineStr">
+        <is>
+          <t>위연 참살</t>
+        </is>
+      </c>
+      <c r="O64" s="10" t="inlineStr">
+        <is>
+          <t>자기보다 레벨이 높은 적에게 주는 피해 20% 증가.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
@@ -4328,7 +4916,7 @@
           <t>남만왕</t>
         </is>
       </c>
-      <c r="J65" s="10" t="inlineStr">
+      <c r="J65" s="11" t="inlineStr">
         <is>
           <t>physicalPower</t>
         </is>
@@ -4344,6 +4932,16 @@
       <c r="M65" s="9" t="inlineStr">
         <is>
           <t>퇴각 대신 1회 체력 50%로 버팀</t>
+        </is>
+      </c>
+      <c r="N65" s="10" t="inlineStr">
+        <is>
+          <t>칠종칠금</t>
+        </is>
+      </c>
+      <c r="O65" s="10" t="inlineStr">
+        <is>
+          <t>자기 차례마다 최대 체력의 8%를 회복한다.</t>
         </is>
       </c>
     </row>
@@ -4397,6 +4995,16 @@
       <c r="M66" s="9" t="inlineStr">
         <is>
           <t>2칸 거리 공격 가능, 명중 시 이동 불가 1턴</t>
+        </is>
+      </c>
+      <c r="N66" s="10" t="inlineStr">
+        <is>
+          <t>비도</t>
+        </is>
+      </c>
+      <c r="O66" s="10" t="inlineStr">
+        <is>
+          <t>꼭 두 칸 떨어진 적에게 물리 피해 20% 증가, 명중 +15%p.</t>
         </is>
       </c>
     </row>
@@ -4448,6 +5056,12 @@
           <t>반동탁·첫 접전에서 공격 +20%</t>
         </is>
       </c>
+      <c r="N67" s="8" t="inlineStr">
+        <is>
+          <t>게임에 없음 — 만들지 않음</t>
+        </is>
+      </c>
+      <c r="O67" s="8" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
@@ -4497,6 +5111,12 @@
           <t>적을 퇴각시키면 즉시 이동력 +2로 추가 이동</t>
         </is>
       </c>
+      <c r="N68" s="8" t="inlineStr">
+        <is>
+          <t>게임에 없음 — 만들지 않음</t>
+        </is>
+      </c>
+      <c r="O68" s="8" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
@@ -4546,6 +5166,12 @@
           <t>일기토 승리 시 상대 진영 1부대 아군으로(설득)</t>
         </is>
       </c>
+      <c r="N69" s="8" t="inlineStr">
+        <is>
+          <t>게임에 없음 — 만들지 않음</t>
+        </is>
+      </c>
+      <c r="O69" s="8" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
@@ -4595,6 +5221,12 @@
           <t>인접 오 장수 방어 +15%</t>
         </is>
       </c>
+      <c r="N70" s="8" t="inlineStr">
+        <is>
+          <t>게임에 없음 — 만들지 않음</t>
+        </is>
+      </c>
+      <c r="O70" s="8" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
@@ -4644,6 +5276,12 @@
           <t>손권·주군 인접 시 대신 공격을 받고 피해 -30%</t>
         </is>
       </c>
+      <c r="N71" s="8" t="inlineStr">
+        <is>
+          <t>게임에 없음 — 만들지 않음</t>
+        </is>
+      </c>
+      <c r="O71" s="8" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
@@ -4693,6 +5331,12 @@
           <t>감녕 인접 시 공격 +20%</t>
         </is>
       </c>
+      <c r="N72" s="8" t="inlineStr">
+        <is>
+          <t>게임에 없음 — 만들지 않음</t>
+        </is>
+      </c>
+      <c r="O72" s="8" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
@@ -4750,6 +5394,16 @@
           <t>전투 시작 시 가짜 성벽 2칸 설치</t>
         </is>
       </c>
+      <c r="N73" s="10" t="inlineStr">
+        <is>
+          <t>의성</t>
+        </is>
+      </c>
+      <c r="O73" s="10" t="inlineStr">
+        <is>
+          <t>전투 첫 세 턴 동안 받는 피해 25% 감소.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
@@ -4807,6 +5461,16 @@
           <t>눈·비 날씨에 공격 +25%</t>
         </is>
       </c>
+      <c r="N74" s="10" t="inlineStr">
+        <is>
+          <t>설중분전</t>
+        </is>
+      </c>
+      <c r="O74" s="10" t="inlineStr">
+        <is>
+          <t>턴이 지날수록 주는 피해가 턴마다 3%씩 증가(최대 24%).</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
@@ -4864,6 +5528,16 @@
           <t>설득 성공률 +15%, 제갈량에게 설전 피해 -30%</t>
         </is>
       </c>
+      <c r="N75" s="10" t="inlineStr">
+        <is>
+          <t>형제의 외교</t>
+        </is>
+      </c>
+      <c r="O75" s="10" t="inlineStr">
+        <is>
+          <t>자신과 곁에 붙은 아군이 받는 책략 피해 12% 감소.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n">
@@ -4919,6 +5593,16 @@
       <c r="M76" s="9" t="inlineStr">
         <is>
           <t>전투 승리 보상 금 +20%</t>
+        </is>
+      </c>
+      <c r="N76" s="10" t="inlineStr">
+        <is>
+          <t>강동 내정</t>
+        </is>
+      </c>
+      <c r="O76" s="10" t="inlineStr">
+        <is>
+          <t>2칸 안 아군의 책략 피해 10% 증가.</t>
         </is>
       </c>
     </row>
@@ -4970,6 +5654,12 @@
           <t>아군 부대 수가 적보다 많으면 전체 공격 +10%</t>
         </is>
       </c>
+      <c r="N77" s="8" t="inlineStr">
+        <is>
+          <t>게임에 없음 — 만들지 않음</t>
+        </is>
+      </c>
+      <c r="O77" s="8" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="n">
@@ -5011,7 +5701,7 @@
           <t>하북 명장</t>
         </is>
       </c>
-      <c r="J78" s="10" t="inlineStr">
+      <c r="J78" s="11" t="inlineStr">
         <is>
           <t>physicalPower</t>
         </is>
@@ -5027,6 +5717,16 @@
       <c r="M78" s="9" t="inlineStr">
         <is>
           <t>첫 일기토 무력 +10</t>
+        </is>
+      </c>
+      <c r="N78" s="10" t="inlineStr">
+        <is>
+          <t>하북의 창</t>
+        </is>
+      </c>
+      <c r="O78" s="10" t="inlineStr">
+        <is>
+          <t>보병·창병을 치면 피해 25% 증가.</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5770,7 @@
           <t>하북 명장</t>
         </is>
       </c>
-      <c r="J79" s="10" t="inlineStr">
+      <c r="J79" s="11" t="inlineStr">
         <is>
           <t>physicalPower</t>
         </is>
@@ -5086,6 +5786,16 @@
       <c r="M79" s="9" t="inlineStr">
         <is>
           <t>기병일 때 돌진 피해 +15%</t>
+        </is>
+      </c>
+      <c r="N79" s="10" t="inlineStr">
+        <is>
+          <t>하북의 칼</t>
+        </is>
+      </c>
+      <c r="O79" s="10" t="inlineStr">
+        <is>
+          <t>궁병·노병 같은 원거리 부대를 치면 피해 25% 증가.</t>
         </is>
       </c>
     </row>
@@ -5137,6 +5847,12 @@
           <t>적 장수를 퇴각시키면 적 전체 사기 저하(공격 -10%, 2턴)</t>
         </is>
       </c>
+      <c r="N80" s="8" t="inlineStr">
+        <is>
+          <t>게임에 없음 — 만들지 않음</t>
+        </is>
+      </c>
+      <c r="O80" s="8" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
@@ -5182,6 +5898,12 @@
           <t>관문 칸에서 공격 +20%</t>
         </is>
       </c>
+      <c r="N81" s="8" t="inlineStr">
+        <is>
+          <t>게임에 없음 — 만들지 않음</t>
+        </is>
+      </c>
+      <c r="O81" s="8" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
@@ -5231,6 +5953,12 @@
           <t>아군 기병 전원 이동력 +1</t>
         </is>
       </c>
+      <c r="N82" s="8" t="inlineStr">
+        <is>
+          <t>게임에 없음 — 만들지 않음</t>
+        </is>
+      </c>
+      <c r="O82" s="8" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="n">
@@ -5276,6 +6004,12 @@
           <t>매 턴 아군 황건 부대 체력 10% 회복</t>
         </is>
       </c>
+      <c r="N83" s="8" t="inlineStr">
+        <is>
+          <t>게임에 없음 — 만들지 않음</t>
+        </is>
+      </c>
+      <c r="O83" s="8" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n">
@@ -5321,6 +6055,12 @@
           <t>보병일 때 성·진지 공격 피해 +30%</t>
         </is>
       </c>
+      <c r="N84" s="8" t="inlineStr">
+        <is>
+          <t>게임에 없음 — 만들지 않음</t>
+        </is>
+      </c>
+      <c r="O84" s="8" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="n">
@@ -5370,6 +6110,12 @@
           <t>아군 기병 공격 +10%</t>
         </is>
       </c>
+      <c r="N85" s="8" t="inlineStr">
+        <is>
+          <t>게임에 없음 — 만들지 않음</t>
+        </is>
+      </c>
+      <c r="O85" s="8" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="n">
@@ -5411,7 +6157,7 @@
           <t>감군</t>
         </is>
       </c>
-      <c r="J86" s="10" t="inlineStr">
+      <c r="J86" s="11" t="inlineStr">
         <is>
           <t>strategyPower</t>
         </is>
@@ -5427,6 +6173,16 @@
       <c r="M86" s="9" t="inlineStr">
         <is>
           <t>아군 책략 회피 +15%</t>
+        </is>
+      </c>
+      <c r="N86" s="10" t="inlineStr">
+        <is>
+          <t>감군</t>
+        </is>
+      </c>
+      <c r="O86" s="10" t="inlineStr">
+        <is>
+          <t>2칸 안 아군의 명중 +10%p.</t>
         </is>
       </c>
     </row>
@@ -5474,7 +6230,7 @@
           <t>직간</t>
         </is>
       </c>
-      <c r="J87" s="10" t="inlineStr">
+      <c r="J87" s="11" t="inlineStr">
         <is>
           <t>strategicGuard</t>
         </is>
@@ -5490,6 +6246,16 @@
       <c r="M87" s="9" t="inlineStr">
         <is>
           <t>적 매복·계략 1회 무효</t>
+        </is>
+      </c>
+      <c r="N87" s="10" t="inlineStr">
+        <is>
+          <t>직간</t>
+        </is>
+      </c>
+      <c r="O87" s="10" t="inlineStr">
+        <is>
+          <t>받은 책략 피해의 20%를 시전자에게 되돌린다.</t>
         </is>
       </c>
     </row>
@@ -5537,7 +6303,7 @@
           <t>업성 사수</t>
         </is>
       </c>
-      <c r="J88" s="10" t="inlineStr">
+      <c r="J88" s="11" t="inlineStr">
         <is>
           <t>commandDefense</t>
         </is>
@@ -5553,6 +6319,16 @@
       <c r="M88" s="9" t="inlineStr">
         <is>
           <t>성 칸에서 받는 피해 -30%</t>
+        </is>
+      </c>
+      <c r="N88" s="10" t="inlineStr">
+        <is>
+          <t>업성 사수</t>
+        </is>
+      </c>
+      <c r="O88" s="10" t="inlineStr">
+        <is>
+          <t>체력이 많을수록 받는 피해 감소(가득하면 20%).</t>
         </is>
       </c>
     </row>
@@ -5604,6 +6380,12 @@
           <t>인접 아군 매 턴 MP +3</t>
         </is>
       </c>
+      <c r="N89" s="8" t="inlineStr">
+        <is>
+          <t>게임에 없음 — 만들지 않음</t>
+        </is>
+      </c>
+      <c r="O89" s="8" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
@@ -5663,6 +6445,16 @@
           <t>물가를 등지면 아군 전원 공격 +20%</t>
         </is>
       </c>
+      <c r="N90" s="10" t="inlineStr">
+        <is>
+          <t>배수진</t>
+        </is>
+      </c>
+      <c r="O90" s="10" t="inlineStr">
+        <is>
+          <t>물을 등지고(물 칸 위나 옆) 싸우면 주는 피해 25% 증가.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
@@ -5708,7 +6500,7 @@
           <t>운주유악</t>
         </is>
       </c>
-      <c r="J91" s="10" t="inlineStr">
+      <c r="J91" s="11" t="inlineStr">
         <is>
           <t>strategyPower</t>
         </is>
@@ -5724,6 +6516,16 @@
       <c r="M91" s="9" t="inlineStr">
         <is>
           <t>전장 어디서든 아군 1명 재행동(3턴마다)</t>
+        </is>
+      </c>
+      <c r="N91" s="10" t="inlineStr">
+        <is>
+          <t>운주유악</t>
+        </is>
+      </c>
+      <c r="O91" s="10" t="inlineStr">
+        <is>
+          <t>2칸 안 아군의 회심 확률 +8%p.</t>
         </is>
       </c>
     </row>
@@ -5785,6 +6587,16 @@
           <t>아군 구급약 +1, 매 턴 아군 체력 5% 회복</t>
         </is>
       </c>
+      <c r="N92" s="10" t="inlineStr">
+        <is>
+          <t>관중 경영</t>
+        </is>
+      </c>
+      <c r="O92" s="10" t="inlineStr">
+        <is>
+          <t>자기 차례마다 3칸 안에서 체력이 가장 낮은 아군 하나를 최대 체력의 12% 회복한다.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
@@ -5826,7 +6638,7 @@
           <t>옥결</t>
         </is>
       </c>
-      <c r="J93" s="10" t="inlineStr">
+      <c r="J93" s="11" t="inlineStr">
         <is>
           <t>strategyPower</t>
         </is>
@@ -5842,6 +6654,16 @@
       <c r="M93" s="9" t="inlineStr">
         <is>
           <t>적 총대장에게 책략 피해 +30%</t>
+        </is>
+      </c>
+      <c r="N93" s="10" t="inlineStr">
+        <is>
+          <t>옥결</t>
+        </is>
+      </c>
+      <c r="O93" s="10" t="inlineStr">
+        <is>
+          <t>이름있는 적 장수에게 주는 책략 피해 25% 증가.</t>
         </is>
       </c>
     </row>
@@ -5885,7 +6707,7 @@
           <t>경형의 맹장</t>
         </is>
       </c>
-      <c r="J94" s="10" t="inlineStr">
+      <c r="J94" s="11" t="inlineStr">
         <is>
           <t>physicalPower</t>
         </is>
@@ -5901,6 +6723,16 @@
       <c r="M94" s="9" t="inlineStr">
         <is>
           <t>공격 후 50% 확률로 추가 이동 2칸</t>
+        </is>
+      </c>
+      <c r="N94" s="10" t="inlineStr">
+        <is>
+          <t>경형의 맹장</t>
+        </is>
+      </c>
+      <c r="O94" s="10" t="inlineStr">
+        <is>
+          <t>물리 공격으로 입힌 피해의 15%만큼 체력을 회복한다.</t>
         </is>
       </c>
     </row>
@@ -5966,6 +6798,16 @@
           <t>공격 후 원래 칸으로 돌아감</t>
         </is>
       </c>
+      <c r="N95" s="10" t="inlineStr">
+        <is>
+          <t>유격</t>
+        </is>
+      </c>
+      <c r="O95" s="10" t="inlineStr">
+        <is>
+          <t>숲·갈대늪 칸에서 회피 +20%p.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
@@ -6025,6 +6867,16 @@
           <t>유방·주군 인접 시 대신 공격을 받음</t>
         </is>
       </c>
+      <c r="N96" s="10" t="inlineStr">
+        <is>
+          <t>홍문의 방패</t>
+        </is>
+      </c>
+      <c r="O96" s="10" t="inlineStr">
+        <is>
+          <t>곁에 붙은 아군의 피해를 대신 받는다(관통 공격 제외). 받는 물리 피해 10% 감소.</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
@@ -6084,6 +6936,16 @@
           <t>적 책사 1명 2턴 행동 불가(전투당 1회)</t>
         </is>
       </c>
+      <c r="N97" s="10" t="inlineStr">
+        <is>
+          <t>반간계</t>
+        </is>
+      </c>
+      <c r="O97" s="10" t="inlineStr">
+        <is>
+          <t>세 턴마다 자기 차례에 3칸 안에서 지력이 가장 높은 적 하나를 혼란에 빠뜨린다.</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
@@ -6137,6 +6999,16 @@
           <t>항우 인접 시 공격 +15%</t>
         </is>
       </c>
+      <c r="N98" s="10" t="inlineStr">
+        <is>
+          <t>고군분투</t>
+        </is>
+      </c>
+      <c r="O98" s="10" t="inlineStr">
+        <is>
+          <t>전장에 남은 아군이 셋 이하이면 주는 피해 20% 증가, 받는 피해 20% 감소.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
@@ -6178,7 +7050,7 @@
           <t>일낙천금</t>
         </is>
       </c>
-      <c r="J99" s="10" t="inlineStr">
+      <c r="J99" s="11" t="inlineStr">
         <is>
           <t>veteran</t>
         </is>
@@ -6196,9 +7068,19 @@
           <t>전투 중 1회 퇴각 위기 아군에게 방어 +40%</t>
         </is>
       </c>
+      <c r="N99" s="10" t="inlineStr">
+        <is>
+          <t>계포일낙</t>
+        </is>
+      </c>
+      <c r="O99" s="10" t="inlineStr">
+        <is>
+          <t>자기 차례마다 2칸 안에서 체력이 절반 이하인 아군을 견고하게 한다(받는 피해 감소).</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M99"/>
+  <autoFilter ref="A4:O99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6229,1809 +7111,1809 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>번호</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>게임 id</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>한 줄 인물평</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>현재 능력(무/지/통/정/매)</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>현재 고유능력</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="n">
+      <c r="A4" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>사마랑</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>sima_lang</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>백달 · 사마팔달의 맏이</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>38/76/56/82/78</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr"/>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="F4" s="13" t="inlineStr"/>
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>이야기 필수 인물(사마의 일가) — 장수 유지 검토</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="n">
+      <c r="A5" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>사마방</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>sima_fang</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>엄정한 가장 · 경조윤</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>42/72/60/80/72</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr"/>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr"/>
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>이야기 필수 인물(사마의 일가) — 장수 유지 검토</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="n">
+      <c r="A6" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>조휴</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>cao_xiu</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>천리구 · 석정에서 꾀에 빠지다</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>76/58/74/52/66</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr"/>
-      <c r="G6" s="12" t="inlineStr"/>
+      <c r="F6" s="13" t="inlineStr"/>
+      <c r="G6" s="13" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="n">
+      <c r="A7" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>조상</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>cao_shuang</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>고평릉에서 모든 것을 잃은 대장군</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>48/38/46/42/52</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr"/>
-      <c r="G7" s="12" t="inlineStr"/>
+      <c r="F7" s="13" t="inlineStr"/>
+      <c r="G7" s="13" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="n">
+      <c r="A8" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>왕릉</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>wang_ling</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>수춘에서 일어난 노신</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>72/74/80/76/76</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr"/>
-      <c r="G8" s="12" t="inlineStr"/>
+      <c r="F8" s="13" t="inlineStr"/>
+      <c r="G8" s="13" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="n">
+      <c r="A9" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>맹달</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>meng_da</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>세 번 주인을 바꾼 신성 태수</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>76/66/72/58/46</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr"/>
-      <c r="G9" s="12" t="inlineStr"/>
+      <c r="F9" s="13" t="inlineStr"/>
+      <c r="G9" s="13" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="n">
+      <c r="A10" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>양앙</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>yang_ang</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>장로의 양평관 수비장</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>70/38/60/28/40</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr"/>
-      <c r="G10" s="12" t="inlineStr"/>
+      <c r="F10" s="13" t="inlineStr"/>
+      <c r="G10" s="13" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="n">
+      <c r="A11" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>고상</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>gao_xiang</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>촉의 군량 수송장</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>64/48/62/40/50</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr"/>
-      <c r="G11" s="12" t="inlineStr"/>
+      <c r="F11" s="13" t="inlineStr"/>
+      <c r="G11" s="13" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="n">
+      <c r="A12" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>맹염</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>meng_yan</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>오장원의 촉 장수</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>68/46/62/36/46</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr"/>
-      <c r="G12" s="12" t="inlineStr"/>
+      <c r="F12" s="13" t="inlineStr"/>
+      <c r="G12" s="13" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="n">
+      <c r="A13" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>여범</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>lu_fan</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>손책 이래의 수군 원로</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>56/72/70/78/66</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr"/>
-      <c r="G13" s="12" t="inlineStr"/>
+      <c r="F13" s="13" t="inlineStr"/>
+      <c r="G13" s="13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="n">
+      <c r="A14" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>손소</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>sun_shao</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>강노를 이끈 오의 장수</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>78/60/76/48/64</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr"/>
-      <c r="G14" s="12" t="inlineStr"/>
+      <c r="F14" s="13" t="inlineStr"/>
+      <c r="G14" s="13" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="n">
+      <c r="A15" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>장패</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>zhang_ba</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>태산의 호족 출신 장수</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>82/52/76/40/60</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr"/>
-      <c r="G15" s="12" t="inlineStr"/>
+      <c r="F15" s="13" t="inlineStr"/>
+      <c r="G15" s="13" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="n">
+      <c r="A16" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>주연</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>zhu_ran</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>강릉을 지킨 오의 맹장</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>76/62/80/52/64</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr"/>
-      <c r="G16" s="12" t="inlineStr"/>
+      <c r="F16" s="13" t="inlineStr"/>
+      <c r="G16" s="13" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="n">
+      <c r="A17" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>제갈각</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>zhuge_ke</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>재주가 넘친 제갈근의 아들</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>50/88/74/72/58</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr"/>
-      <c r="G17" s="12" t="inlineStr"/>
+      <c r="F17" s="13" t="inlineStr"/>
+      <c r="G17" s="13" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="n">
+      <c r="A18" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>대릉</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>dai_ling</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>오장원의 위 장수</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>70/50/66/38/50</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr"/>
-      <c r="G18" s="12" t="inlineStr"/>
+      <c r="F18" s="13" t="inlineStr"/>
+      <c r="G18" s="13" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="n">
+      <c r="A19" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>고수</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>gao_shou</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>결사대를 이끈 장수</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>72/40/60/30/44</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr"/>
-      <c r="G19" s="12" t="inlineStr"/>
+      <c r="F19" s="13" t="inlineStr"/>
+      <c r="G19" s="13" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="n">
+      <c r="A20" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>공손연</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>gongsun_yuan</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>연왕을 칭한 요동의 주인</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>62/58/66/60/48</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr"/>
-      <c r="G20" s="12" t="inlineStr"/>
+      <c r="F20" s="13" t="inlineStr"/>
+      <c r="G20" s="13" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="n">
+      <c r="A21" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>비연</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>bi_yan</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>공손연의 대장</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>72/50/70/40/50</t>
         </is>
       </c>
-      <c r="F21" s="12" t="inlineStr"/>
-      <c r="G21" s="12" t="inlineStr"/>
+      <c r="F21" s="13" t="inlineStr"/>
+      <c r="G21" s="13" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="n">
+      <c r="A22" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>우희</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>우희</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>우미인 · 패왕과 이별한 여인</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>30/64/42/62/96</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
+      <c r="F22" s="13" t="inlineStr">
         <is>
           <t>검무</t>
         </is>
       </c>
-      <c r="G22" s="12" t="inlineStr">
+      <c r="G22" s="13" t="inlineStr">
         <is>
           <t>초한 인물(장수 아님)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="n">
+      <c r="A23" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>용저</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>용저</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>초의 맹장 · 유수에서 한신에게 지다</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>90/40/80/30/52</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr"/>
-      <c r="G23" s="12" t="inlineStr"/>
+      <c r="F23" s="13" t="inlineStr"/>
+      <c r="G23" s="13" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="n">
+      <c r="A24" s="13" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>조참</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>조참</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>소규조수 · 소하를 이은 상국</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>80/72/84/88/74</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr"/>
-      <c r="G24" s="12" t="inlineStr"/>
+      <c r="F24" s="13" t="inlineStr"/>
+      <c r="G24" s="13" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="n">
+      <c r="A25" s="13" t="n">
         <v>22</v>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>관영</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>관영</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>낭중기를 이끈 기병장</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>86/58/84/52/66</t>
         </is>
       </c>
-      <c r="F25" s="12" t="inlineStr">
+      <c r="F25" s="13" t="inlineStr">
         <is>
           <t>낭중 돌격</t>
         </is>
       </c>
-      <c r="G25" s="12" t="inlineStr"/>
+      <c r="G25" s="13" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="n">
+      <c r="A26" s="13" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>원담</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>원담</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>원소의 맏아들</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>68/48/62/40/52</t>
         </is>
       </c>
-      <c r="F26" s="12" t="inlineStr"/>
-      <c r="G26" s="12" t="inlineStr"/>
+      <c r="F26" s="13" t="inlineStr"/>
+      <c r="G26" s="13" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="n">
+      <c r="A27" s="13" t="n">
         <v>24</v>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>고람</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>고람</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>원씨의 하북 명장</t>
         </is>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>80/50/74/40/52</t>
         </is>
       </c>
-      <c r="F27" s="12" t="inlineStr"/>
-      <c r="G27" s="12" t="inlineStr"/>
+      <c r="F27" s="13" t="inlineStr"/>
+      <c r="G27" s="13" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="n">
+      <c r="A28" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>조식</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>조식</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>칠보시의 공자 · 시를 사랑한 왕</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>24/90/40/72/86</t>
         </is>
       </c>
-      <c r="F28" s="12" t="inlineStr"/>
-      <c r="G28" s="12" t="inlineStr"/>
+      <c r="F28" s="13" t="inlineStr"/>
+      <c r="G28" s="13" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="n">
+      <c r="A29" s="13" t="n">
         <v>26</v>
       </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>조예</t>
         </is>
       </c>
-      <c r="C29" s="12" t="inlineStr">
+      <c r="C29" s="13" t="inlineStr">
         <is>
           <t>조예</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
         <is>
           <t>위 명제 · 영민한 황제</t>
         </is>
       </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>42/84/74/82/78</t>
         </is>
       </c>
-      <c r="F29" s="12" t="inlineStr"/>
-      <c r="G29" s="12" t="inlineStr"/>
+      <c r="F29" s="13" t="inlineStr"/>
+      <c r="G29" s="13" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="n">
+      <c r="A30" s="13" t="n">
         <v>27</v>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>올돌골</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="C30" s="13" t="inlineStr">
         <is>
           <t>올돌골</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>오과국 왕 · 등갑군의 주인</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>88/22/70/10/40</t>
         </is>
       </c>
-      <c r="F30" s="12" t="inlineStr">
+      <c r="F30" s="13" t="inlineStr">
         <is>
           <t>등갑</t>
         </is>
       </c>
-      <c r="G30" s="12" t="inlineStr"/>
+      <c r="G30" s="13" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="n">
+      <c r="A31" s="13" t="n">
         <v>28</v>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>봉기</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr">
+      <c r="C31" s="13" t="inlineStr">
         <is>
           <t>봉기</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>원씨의 직언가</t>
         </is>
       </c>
-      <c r="E31" s="12" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>40/80/60/72/58</t>
         </is>
       </c>
-      <c r="F31" s="12" t="inlineStr"/>
-      <c r="G31" s="12" t="inlineStr"/>
+      <c r="F31" s="13" t="inlineStr"/>
+      <c r="G31" s="13" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="n">
+      <c r="A32" s="13" t="n">
         <v>29</v>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
         <is>
           <t>원상</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C32" s="13" t="inlineStr">
         <is>
           <t>원상</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D32" s="13" t="inlineStr">
         <is>
           <t>원소의 셋째 아들 · 하북의 후계</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="13" t="inlineStr">
         <is>
           <t>72/58/70/52/74</t>
         </is>
       </c>
-      <c r="F32" s="12" t="inlineStr"/>
-      <c r="G32" s="12" t="inlineStr"/>
+      <c r="F32" s="13" t="inlineStr"/>
+      <c r="G32" s="13" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="n">
+      <c r="A33" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>고간</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C33" s="13" t="inlineStr">
         <is>
           <t>고간</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>원소의 조카 · 병주 자사</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>70/52/68/48/54</t>
         </is>
       </c>
-      <c r="F33" s="12" t="inlineStr"/>
-      <c r="G33" s="12" t="inlineStr"/>
+      <c r="F33" s="13" t="inlineStr"/>
+      <c r="G33" s="13" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="n">
+      <c r="A34" s="13" t="n">
         <v>31</v>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>답돈</t>
         </is>
       </c>
-      <c r="C34" s="12" t="inlineStr">
+      <c r="C34" s="13" t="inlineStr">
         <is>
           <t>답돈</t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t>오환의 선우 · 백랑산의 기병</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="13" t="inlineStr">
         <is>
           <t>84/40/78/30/62</t>
         </is>
       </c>
-      <c r="F34" s="12" t="inlineStr">
+      <c r="F34" s="13" t="inlineStr">
         <is>
           <t>오환 돌기</t>
         </is>
       </c>
-      <c r="G34" s="12" t="inlineStr"/>
+      <c r="G34" s="13" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="n">
+      <c r="A35" s="13" t="n">
         <v>32</v>
       </c>
-      <c r="B35" s="12" t="inlineStr">
+      <c r="B35" s="13" t="inlineStr">
         <is>
           <t>환범</t>
         </is>
       </c>
-      <c r="C35" s="12" t="inlineStr">
+      <c r="C35" s="13" t="inlineStr">
         <is>
           <t>환범</t>
         </is>
       </c>
-      <c r="D35" s="12" t="inlineStr">
+      <c r="D35" s="13" t="inlineStr">
         <is>
           <t>지낭 · 조상의 꾀주머니</t>
         </is>
       </c>
-      <c r="E35" s="12" t="inlineStr">
+      <c r="E35" s="13" t="inlineStr">
         <is>
           <t>30/84/40/80/60</t>
         </is>
       </c>
-      <c r="F35" s="12" t="inlineStr"/>
-      <c r="G35" s="12" t="inlineStr"/>
+      <c r="F35" s="13" t="inlineStr"/>
+      <c r="G35" s="13" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="12" t="n">
+      <c r="A36" s="13" t="n">
         <v>33</v>
       </c>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>하안</t>
         </is>
       </c>
-      <c r="C36" s="12" t="inlineStr">
+      <c r="C36" s="13" t="inlineStr">
         <is>
           <t>하안</t>
         </is>
       </c>
-      <c r="D36" s="12" t="inlineStr">
+      <c r="D36" s="13" t="inlineStr">
         <is>
           <t>부분 바른 미남 · 조상의 심복</t>
         </is>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>20/76/30/70/68</t>
         </is>
       </c>
-      <c r="F36" s="12" t="inlineStr"/>
-      <c r="G36" s="12" t="inlineStr"/>
+      <c r="F36" s="13" t="inlineStr"/>
+      <c r="G36" s="13" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="n">
+      <c r="A37" s="13" t="n">
         <v>34</v>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B37" s="13" t="inlineStr">
         <is>
           <t>조희</t>
         </is>
       </c>
-      <c r="C37" s="12" t="inlineStr">
+      <c r="C37" s="13" t="inlineStr">
         <is>
           <t>조희</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="D37" s="13" t="inlineStr">
         <is>
           <t>조상의 아우 · 중령군</t>
         </is>
       </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="E37" s="13" t="inlineStr">
         <is>
           <t>60/40/55/40/48</t>
         </is>
       </c>
-      <c r="F37" s="12" t="inlineStr"/>
-      <c r="G37" s="12" t="inlineStr"/>
+      <c r="F37" s="13" t="inlineStr"/>
+      <c r="G37" s="13" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="12" t="n">
+      <c r="A38" s="13" t="n">
         <v>35</v>
       </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B38" s="13" t="inlineStr">
         <is>
           <t>진태</t>
         </is>
       </c>
-      <c r="C38" s="12" t="inlineStr">
+      <c r="C38" s="13" t="inlineStr">
         <is>
           <t>진태</t>
         </is>
       </c>
-      <c r="D38" s="12" t="inlineStr">
+      <c r="D38" s="13" t="inlineStr">
         <is>
           <t>진군의 아들 · 옹주를 지킨 장수</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E38" s="13" t="inlineStr">
         <is>
           <t>78/78/84/72/72</t>
         </is>
       </c>
-      <c r="F38" s="12" t="inlineStr"/>
-      <c r="G38" s="12" t="inlineStr"/>
+      <c r="F38" s="13" t="inlineStr"/>
+      <c r="G38" s="13" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="12" t="n">
+      <c r="A39" s="13" t="n">
         <v>36</v>
       </c>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B39" s="13" t="inlineStr">
         <is>
           <t>손례</t>
         </is>
       </c>
-      <c r="C39" s="12" t="inlineStr">
+      <c r="C39" s="13" t="inlineStr">
         <is>
           <t>손례</t>
         </is>
       </c>
-      <c r="D39" s="12" t="inlineStr">
+      <c r="D39" s="13" t="inlineStr">
         <is>
           <t>맨손으로 범을 막은 장수</t>
         </is>
       </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="E39" s="13" t="inlineStr">
         <is>
           <t>80/58/78/62/64</t>
         </is>
       </c>
-      <c r="F39" s="12" t="inlineStr"/>
-      <c r="G39" s="12" t="inlineStr"/>
+      <c r="F39" s="13" t="inlineStr"/>
+      <c r="G39" s="13" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="12" t="n">
+      <c r="A40" s="13" t="n">
         <v>37</v>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B40" s="13" t="inlineStr">
         <is>
           <t>왕기</t>
         </is>
       </c>
-      <c r="C40" s="12" t="inlineStr">
+      <c r="C40" s="13" t="inlineStr">
         <is>
           <t>왕기</t>
         </is>
       </c>
-      <c r="D40" s="12" t="inlineStr">
+      <c r="D40" s="13" t="inlineStr">
         <is>
           <t>관구검의 난을 막은 장수</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E40" s="13" t="inlineStr">
         <is>
           <t>72/74/80/70/64</t>
         </is>
       </c>
-      <c r="F40" s="12" t="inlineStr"/>
-      <c r="G40" s="12" t="inlineStr"/>
+      <c r="F40" s="13" t="inlineStr"/>
+      <c r="G40" s="13" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="12" t="n">
+      <c r="A41" s="13" t="n">
         <v>38</v>
       </c>
-      <c r="B41" s="12" t="inlineStr">
+      <c r="B41" s="13" t="inlineStr">
         <is>
           <t>문흠</t>
         </is>
       </c>
-      <c r="C41" s="12" t="inlineStr">
+      <c r="C41" s="13" t="inlineStr">
         <is>
           <t>문흠</t>
         </is>
       </c>
-      <c r="D41" s="12" t="inlineStr">
+      <c r="D41" s="13" t="inlineStr">
         <is>
           <t>수춘에서 난을 일으킨 맹장</t>
         </is>
       </c>
-      <c r="E41" s="12" t="inlineStr">
+      <c r="E41" s="13" t="inlineStr">
         <is>
           <t>84/40/70/30/46</t>
         </is>
       </c>
-      <c r="F41" s="12" t="inlineStr">
+      <c r="F41" s="13" t="inlineStr">
         <is>
           <t>수춘 돌파</t>
         </is>
       </c>
-      <c r="G41" s="12" t="inlineStr"/>
+      <c r="G41" s="13" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="12" t="n">
+      <c r="A42" s="13" t="n">
         <v>39</v>
       </c>
-      <c r="B42" s="12" t="inlineStr">
+      <c r="B42" s="13" t="inlineStr">
         <is>
           <t>가규</t>
         </is>
       </c>
-      <c r="C42" s="12" t="inlineStr">
+      <c r="C42" s="13" t="inlineStr">
         <is>
           <t>가규</t>
         </is>
       </c>
-      <c r="D42" s="12" t="inlineStr">
+      <c r="D42" s="13" t="inlineStr">
         <is>
           <t>예주를 다스린 충신</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="E42" s="13" t="inlineStr">
         <is>
           <t>64/78/76/84/72</t>
         </is>
       </c>
-      <c r="F42" s="12" t="inlineStr"/>
-      <c r="G42" s="12" t="inlineStr"/>
+      <c r="F42" s="13" t="inlineStr"/>
+      <c r="G42" s="13" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="12" t="n">
+      <c r="A43" s="13" t="n">
         <v>40</v>
       </c>
-      <c r="B43" s="12" t="inlineStr">
+      <c r="B43" s="13" t="inlineStr">
         <is>
           <t>호준</t>
         </is>
       </c>
-      <c r="C43" s="12" t="inlineStr">
+      <c r="C43" s="13" t="inlineStr">
         <is>
           <t>호준</t>
         </is>
       </c>
-      <c r="D43" s="12" t="inlineStr">
+      <c r="D43" s="13" t="inlineStr">
         <is>
           <t>사마의의 오랜 부장</t>
         </is>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E43" s="13" t="inlineStr">
         <is>
           <t>74/56/76/52/62</t>
         </is>
       </c>
-      <c r="F43" s="12" t="inlineStr"/>
-      <c r="G43" s="12" t="inlineStr"/>
+      <c r="F43" s="13" t="inlineStr"/>
+      <c r="G43" s="13" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="12" t="n">
+      <c r="A44" s="13" t="n">
         <v>41</v>
       </c>
-      <c r="B44" s="12" t="inlineStr">
+      <c r="B44" s="13" t="inlineStr">
         <is>
           <t>견초</t>
         </is>
       </c>
-      <c r="C44" s="12" t="inlineStr">
+      <c r="C44" s="13" t="inlineStr">
         <is>
           <t>견초</t>
         </is>
       </c>
-      <c r="D44" s="12" t="inlineStr">
+      <c r="D44" s="13" t="inlineStr">
         <is>
           <t>조조 휘하의 기병장</t>
         </is>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="E44" s="13" t="inlineStr">
         <is>
           <t>72/48/66/40/52</t>
         </is>
       </c>
-      <c r="F44" s="12" t="inlineStr"/>
-      <c r="G44" s="12" t="inlineStr"/>
+      <c r="F44" s="13" t="inlineStr"/>
+      <c r="G44" s="13" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="12" t="n">
+      <c r="A45" s="13" t="n">
         <v>42</v>
       </c>
-      <c r="B45" s="12" t="inlineStr">
+      <c r="B45" s="13" t="inlineStr">
         <is>
           <t>전주</t>
         </is>
       </c>
-      <c r="C45" s="12" t="inlineStr">
+      <c r="C45" s="13" t="inlineStr">
         <is>
           <t>전주</t>
         </is>
       </c>
-      <c r="D45" s="12" t="inlineStr">
+      <c r="D45" s="13" t="inlineStr">
         <is>
           <t>무종의 은사 · 백랑산의 길잡이</t>
         </is>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E45" s="13" t="inlineStr">
         <is>
           <t>70/76/72/70/74</t>
         </is>
       </c>
-      <c r="F45" s="12" t="inlineStr"/>
-      <c r="G45" s="12" t="inlineStr"/>
+      <c r="F45" s="13" t="inlineStr"/>
+      <c r="G45" s="13" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="12" t="n">
+      <c r="A46" s="13" t="n">
         <v>43</v>
       </c>
-      <c r="B46" s="12" t="inlineStr">
+      <c r="B46" s="13" t="inlineStr">
         <is>
           <t>채모</t>
         </is>
       </c>
-      <c r="C46" s="12" t="inlineStr">
+      <c r="C46" s="13" t="inlineStr">
         <is>
           <t>채모</t>
         </is>
       </c>
-      <c r="D46" s="12" t="inlineStr">
+      <c r="D46" s="13" t="inlineStr">
         <is>
           <t>형주 수군의 대도독</t>
         </is>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E46" s="13" t="inlineStr">
         <is>
           <t>72/66/78/62/54</t>
         </is>
       </c>
-      <c r="F46" s="12" t="inlineStr"/>
-      <c r="G46" s="12" t="inlineStr"/>
+      <c r="F46" s="13" t="inlineStr"/>
+      <c r="G46" s="13" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="12" t="n">
+      <c r="A47" s="13" t="n">
         <v>44</v>
       </c>
-      <c r="B47" s="12" t="inlineStr">
+      <c r="B47" s="13" t="inlineStr">
         <is>
           <t>서서</t>
         </is>
       </c>
-      <c r="C47" s="12" t="inlineStr">
+      <c r="C47" s="13" t="inlineStr">
         <is>
           <t>서서</t>
         </is>
       </c>
-      <c r="D47" s="12" t="inlineStr">
+      <c r="D47" s="13" t="inlineStr">
         <is>
           <t>단복 · 유비를 떠난 효자</t>
         </is>
       </c>
-      <c r="E47" s="12" t="inlineStr">
+      <c r="E47" s="13" t="inlineStr">
         <is>
           <t>66/92/80/80/82</t>
         </is>
       </c>
-      <c r="F47" s="12" t="inlineStr">
+      <c r="F47" s="13" t="inlineStr">
         <is>
           <t>팔문금쇄 간파</t>
         </is>
       </c>
-      <c r="G47" s="12" t="inlineStr"/>
+      <c r="G47" s="13" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="12" t="n">
+      <c r="A48" s="13" t="n">
         <v>45</v>
       </c>
-      <c r="B48" s="12" t="inlineStr">
+      <c r="B48" s="13" t="inlineStr">
         <is>
           <t>사마부</t>
         </is>
       </c>
-      <c r="C48" s="12" t="inlineStr">
+      <c r="C48" s="13" t="inlineStr">
         <is>
           <t>사마부</t>
         </is>
       </c>
-      <c r="D48" s="12" t="inlineStr">
+      <c r="D48" s="13" t="inlineStr">
         <is>
           <t>숙달 · 사마의의 아우</t>
         </is>
       </c>
-      <c r="E48" s="12" t="inlineStr">
+      <c r="E48" s="13" t="inlineStr">
         <is>
           <t>48/80/72/90/82</t>
         </is>
       </c>
-      <c r="F48" s="12" t="inlineStr"/>
-      <c r="G48" s="12" t="inlineStr">
+      <c r="F48" s="13" t="inlineStr"/>
+      <c r="G48" s="13" t="inlineStr">
         <is>
           <t>이야기 필수 인물(사마의 일가) — 장수 유지 검토</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="12" t="n">
+      <c r="A49" s="13" t="n">
         <v>46</v>
       </c>
-      <c r="B49" s="12" t="inlineStr">
+      <c r="B49" s="13" t="inlineStr">
         <is>
           <t>양준</t>
         </is>
       </c>
-      <c r="C49" s="12" t="inlineStr">
+      <c r="C49" s="13" t="inlineStr">
         <is>
           <t>양준</t>
         </is>
       </c>
-      <c r="D49" s="12" t="inlineStr">
+      <c r="D49" s="13" t="inlineStr">
         <is>
           <t>하내의 명사</t>
         </is>
       </c>
-      <c r="E49" s="12" t="inlineStr">
+      <c r="E49" s="13" t="inlineStr">
         <is>
           <t>36/78/60/84/78</t>
         </is>
       </c>
-      <c r="F49" s="12" t="inlineStr"/>
-      <c r="G49" s="12" t="inlineStr"/>
+      <c r="F49" s="13" t="inlineStr"/>
+      <c r="G49" s="13" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="12" t="n">
+      <c r="A50" s="13" t="n">
         <v>47</v>
       </c>
-      <c r="B50" s="12" t="inlineStr">
+      <c r="B50" s="13" t="inlineStr">
         <is>
           <t>양수</t>
         </is>
       </c>
-      <c r="C50" s="12" t="inlineStr">
+      <c r="C50" s="13" t="inlineStr">
         <is>
           <t>양수</t>
         </is>
       </c>
-      <c r="D50" s="12" t="inlineStr">
+      <c r="D50" s="13" t="inlineStr">
         <is>
           <t>계륵 · 재주가 넘친 주부</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E50" s="13" t="inlineStr">
         <is>
           <t>30/92/52/74/70</t>
         </is>
       </c>
-      <c r="F50" s="12" t="inlineStr"/>
-      <c r="G50" s="12" t="inlineStr"/>
+      <c r="F50" s="13" t="inlineStr"/>
+      <c r="G50" s="13" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="12" t="n">
+      <c r="A51" s="13" t="n">
         <v>48</v>
       </c>
-      <c r="B51" s="12" t="inlineStr">
+      <c r="B51" s="13" t="inlineStr">
         <is>
           <t>만총</t>
         </is>
       </c>
-      <c r="C51" s="12" t="inlineStr">
+      <c r="C51" s="13" t="inlineStr">
         <is>
           <t>만총</t>
         </is>
       </c>
-      <c r="D51" s="12" t="inlineStr">
+      <c r="D51" s="13" t="inlineStr">
         <is>
           <t>합비 신성의 수장</t>
         </is>
       </c>
-      <c r="E51" s="12" t="inlineStr">
+      <c r="E51" s="13" t="inlineStr">
         <is>
           <t>66/82/86/84/70</t>
         </is>
       </c>
-      <c r="F51" s="12" t="inlineStr"/>
-      <c r="G51" s="12" t="inlineStr"/>
+      <c r="F51" s="13" t="inlineStr"/>
+      <c r="G51" s="13" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="12" t="n">
+      <c r="A52" s="13" t="n">
         <v>49</v>
       </c>
-      <c r="B52" s="12" t="inlineStr">
+      <c r="B52" s="13" t="inlineStr">
         <is>
           <t>가충</t>
         </is>
       </c>
-      <c r="C52" s="12" t="inlineStr">
+      <c r="C52" s="13" t="inlineStr">
         <is>
           <t>가충</t>
         </is>
       </c>
-      <c r="D52" s="12" t="inlineStr">
+      <c r="D52" s="13" t="inlineStr">
         <is>
           <t>사마씨의 심복</t>
         </is>
       </c>
-      <c r="E52" s="12" t="inlineStr">
+      <c r="E52" s="13" t="inlineStr">
         <is>
           <t>50/82/64/78/52</t>
         </is>
       </c>
-      <c r="F52" s="12" t="inlineStr"/>
-      <c r="G52" s="12" t="inlineStr"/>
+      <c r="F52" s="13" t="inlineStr"/>
+      <c r="G52" s="13" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="12" t="n">
+      <c r="A53" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="B53" s="12" t="inlineStr">
+      <c r="B53" s="13" t="inlineStr">
         <is>
           <t>석포</t>
         </is>
       </c>
-      <c r="C53" s="12" t="inlineStr">
+      <c r="C53" s="13" t="inlineStr">
         <is>
           <t>석포</t>
         </is>
       </c>
-      <c r="D53" s="12" t="inlineStr">
+      <c r="D53" s="13" t="inlineStr">
         <is>
           <t>정위의 장수</t>
         </is>
       </c>
-      <c r="E53" s="12" t="inlineStr">
+      <c r="E53" s="13" t="inlineStr">
         <is>
           <t>78/68/80/60/64</t>
         </is>
       </c>
-      <c r="F53" s="12" t="inlineStr"/>
-      <c r="G53" s="12" t="inlineStr"/>
+      <c r="F53" s="13" t="inlineStr"/>
+      <c r="G53" s="13" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="12" t="n">
+      <c r="A54" s="13" t="n">
         <v>51</v>
       </c>
-      <c r="B54" s="12" t="inlineStr">
+      <c r="B54" s="13" t="inlineStr">
         <is>
           <t>유봉</t>
         </is>
       </c>
-      <c r="C54" s="12" t="inlineStr">
+      <c r="C54" s="13" t="inlineStr">
         <is>
           <t>유봉</t>
         </is>
       </c>
-      <c r="D54" s="12" t="inlineStr">
+      <c r="D54" s="13" t="inlineStr">
         <is>
           <t>유비의 양자</t>
         </is>
       </c>
-      <c r="E54" s="12" t="inlineStr">
+      <c r="E54" s="13" t="inlineStr">
         <is>
           <t>80/46/68/40/54</t>
         </is>
       </c>
-      <c r="F54" s="12" t="inlineStr"/>
-      <c r="G54" s="12" t="inlineStr"/>
+      <c r="F54" s="13" t="inlineStr"/>
+      <c r="G54" s="13" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="12" t="n">
+      <c r="A55" s="13" t="n">
         <v>52</v>
       </c>
-      <c r="B55" s="12" t="inlineStr">
+      <c r="B55" s="13" t="inlineStr">
         <is>
           <t>관색</t>
         </is>
       </c>
-      <c r="C55" s="12" t="inlineStr">
+      <c r="C55" s="13" t="inlineStr">
         <is>
           <t>관색</t>
         </is>
       </c>
-      <c r="D55" s="12" t="inlineStr">
+      <c r="D55" s="13" t="inlineStr">
         <is>
           <t>관우의 셋째 아들</t>
         </is>
       </c>
-      <c r="E55" s="12" t="inlineStr">
+      <c r="E55" s="13" t="inlineStr">
         <is>
           <t>84/52/70/40/72</t>
         </is>
       </c>
-      <c r="F55" s="12" t="inlineStr"/>
-      <c r="G55" s="12" t="inlineStr"/>
+      <c r="F55" s="13" t="inlineStr"/>
+      <c r="G55" s="13" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="12" t="n">
+      <c r="A56" s="13" t="n">
         <v>53</v>
       </c>
-      <c r="B56" s="12" t="inlineStr">
+      <c r="B56" s="13" t="inlineStr">
         <is>
           <t>장제</t>
         </is>
       </c>
-      <c r="C56" s="12" t="inlineStr">
+      <c r="C56" s="13" t="inlineStr">
         <is>
           <t>장제</t>
         </is>
       </c>
-      <c r="D56" s="12" t="inlineStr">
+      <c r="D56" s="13" t="inlineStr">
         <is>
           <t>태위 · 사마의의 벗</t>
         </is>
       </c>
-      <c r="E56" s="12" t="inlineStr">
+      <c r="E56" s="13" t="inlineStr">
         <is>
           <t>40/86/70/86/74</t>
         </is>
       </c>
-      <c r="F56" s="12" t="inlineStr"/>
-      <c r="G56" s="12" t="inlineStr"/>
+      <c r="F56" s="13" t="inlineStr"/>
+      <c r="G56" s="13" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="12" t="n">
+      <c r="A57" s="13" t="n">
         <v>54</v>
       </c>
-      <c r="B57" s="12" t="inlineStr">
+      <c r="B57" s="13" t="inlineStr">
         <is>
           <t>왕관</t>
         </is>
       </c>
-      <c r="C57" s="12" t="inlineStr">
+      <c r="C57" s="13" t="inlineStr">
         <is>
           <t>왕관</t>
         </is>
       </c>
-      <c r="D57" s="12" t="inlineStr">
+      <c r="D57" s="13" t="inlineStr">
         <is>
           <t>엄정한 관리</t>
         </is>
       </c>
-      <c r="E57" s="12" t="inlineStr">
+      <c r="E57" s="13" t="inlineStr">
         <is>
           <t>56/72/68/84/60</t>
         </is>
       </c>
-      <c r="F57" s="12" t="inlineStr"/>
-      <c r="G57" s="12" t="inlineStr"/>
+      <c r="F57" s="13" t="inlineStr"/>
+      <c r="G57" s="13" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="12" t="n">
+      <c r="A58" s="13" t="n">
         <v>55</v>
       </c>
-      <c r="B58" s="12" t="inlineStr">
+      <c r="B58" s="13" t="inlineStr">
         <is>
           <t>왕찬</t>
         </is>
       </c>
-      <c r="C58" s="12" t="inlineStr">
+      <c r="C58" s="13" t="inlineStr">
         <is>
           <t>왕찬</t>
         </is>
       </c>
-      <c r="D58" s="12" t="inlineStr">
+      <c r="D58" s="13" t="inlineStr">
         <is>
           <t>건안칠자의 으뜸 · 등루부의 문사</t>
         </is>
       </c>
-      <c r="E58" s="12" t="inlineStr">
+      <c r="E58" s="13" t="inlineStr">
         <is>
           <t>20/86/30/80/72</t>
         </is>
       </c>
-      <c r="F58" s="12" t="inlineStr"/>
-      <c r="G58" s="12" t="inlineStr"/>
+      <c r="F58" s="13" t="inlineStr"/>
+      <c r="G58" s="13" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="12" t="n">
+      <c r="A59" s="13" t="n">
         <v>56</v>
       </c>
-      <c r="B59" s="12" t="inlineStr">
+      <c r="B59" s="13" t="inlineStr">
         <is>
           <t>왕창</t>
         </is>
       </c>
-      <c r="C59" s="12" t="inlineStr">
+      <c r="C59" s="13" t="inlineStr">
         <is>
           <t>왕창</t>
         </is>
       </c>
-      <c r="D59" s="12" t="inlineStr">
+      <c r="D59" s="13" t="inlineStr">
         <is>
           <t>형주를 지킨 위의 장수</t>
         </is>
       </c>
-      <c r="E59" s="12" t="inlineStr">
+      <c r="E59" s="13" t="inlineStr">
         <is>
           <t>70/74/82/76/70</t>
         </is>
       </c>
-      <c r="F59" s="12" t="inlineStr"/>
-      <c r="G59" s="12" t="inlineStr"/>
+      <c r="F59" s="13" t="inlineStr"/>
+      <c r="G59" s="13" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="12" t="n">
+      <c r="A60" s="13" t="n">
         <v>57</v>
       </c>
-      <c r="B60" s="12" t="inlineStr">
+      <c r="B60" s="13" t="inlineStr">
         <is>
           <t>황권</t>
         </is>
       </c>
-      <c r="C60" s="12" t="inlineStr">
+      <c r="C60" s="13" t="inlineStr">
         <is>
           <t>황권</t>
         </is>
       </c>
-      <c r="D60" s="12" t="inlineStr">
+      <c r="D60" s="13" t="inlineStr">
         <is>
           <t>촉에서 위로 온 충신</t>
         </is>
       </c>
-      <c r="E60" s="12" t="inlineStr">
+      <c r="E60" s="13" t="inlineStr">
         <is>
           <t>66/82/78/80/78</t>
         </is>
       </c>
-      <c r="F60" s="12" t="inlineStr"/>
-      <c r="G60" s="12" t="inlineStr"/>
+      <c r="F60" s="13" t="inlineStr"/>
+      <c r="G60" s="13" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="12" t="n">
+      <c r="A61" s="13" t="n">
         <v>58</v>
       </c>
-      <c r="B61" s="12" t="inlineStr">
+      <c r="B61" s="13" t="inlineStr">
         <is>
           <t>하후패</t>
         </is>
       </c>
-      <c r="C61" s="12" t="inlineStr">
+      <c r="C61" s="13" t="inlineStr">
         <is>
           <t>하후패</t>
         </is>
       </c>
-      <c r="D61" s="12" t="inlineStr">
+      <c r="D61" s="13" t="inlineStr">
         <is>
           <t>하후연의 아들</t>
         </is>
       </c>
-      <c r="E61" s="12" t="inlineStr">
+      <c r="E61" s="13" t="inlineStr">
         <is>
           <t>86/52/78/40/62</t>
         </is>
       </c>
-      <c r="F61" s="12" t="inlineStr"/>
-      <c r="G61" s="12" t="inlineStr"/>
+      <c r="F61" s="13" t="inlineStr"/>
+      <c r="G61" s="13" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="12" t="n">
+      <c r="A62" s="13" t="n">
         <v>59</v>
       </c>
-      <c r="B62" s="12" t="inlineStr">
+      <c r="B62" s="13" t="inlineStr">
         <is>
           <t>하후무</t>
         </is>
       </c>
-      <c r="C62" s="12" t="inlineStr">
+      <c r="C62" s="13" t="inlineStr">
         <is>
           <t>하후무</t>
         </is>
       </c>
-      <c r="D62" s="12" t="inlineStr">
+      <c r="D62" s="13" t="inlineStr">
         <is>
           <t>청강의 부마</t>
         </is>
       </c>
-      <c r="E62" s="12" t="inlineStr">
+      <c r="E62" s="13" t="inlineStr">
         <is>
           <t>46/40/40/38/50</t>
         </is>
       </c>
-      <c r="F62" s="12" t="inlineStr"/>
-      <c r="G62" s="12" t="inlineStr"/>
+      <c r="F62" s="13" t="inlineStr"/>
+      <c r="G62" s="13" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="12" t="n">
+      <c r="A63" s="13" t="n">
         <v>60</v>
       </c>
-      <c r="B63" s="12" t="inlineStr">
+      <c r="B63" s="13" t="inlineStr">
         <is>
           <t>타사대왕</t>
         </is>
       </c>
-      <c r="C63" s="12" t="inlineStr">
+      <c r="C63" s="13" t="inlineStr">
         <is>
           <t>타사대왕</t>
         </is>
       </c>
-      <c r="D63" s="12" t="inlineStr">
+      <c r="D63" s="13" t="inlineStr">
         <is>
           <t>독천의 주인</t>
         </is>
       </c>
-      <c r="E63" s="12" t="inlineStr">
+      <c r="E63" s="13" t="inlineStr">
         <is>
           <t>74/52/70/30/46</t>
         </is>
       </c>
-      <c r="F63" s="12" t="inlineStr"/>
-      <c r="G63" s="12" t="inlineStr"/>
+      <c r="F63" s="13" t="inlineStr"/>
+      <c r="G63" s="13" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="12" t="n">
+      <c r="A64" s="13" t="n">
         <v>61</v>
       </c>
-      <c r="B64" s="12" t="inlineStr">
+      <c r="B64" s="13" t="inlineStr">
         <is>
           <t>목록대왕</t>
         </is>
       </c>
-      <c r="C64" s="12" t="inlineStr">
+      <c r="C64" s="13" t="inlineStr">
         <is>
           <t>목록대왕</t>
         </is>
       </c>
-      <c r="D64" s="12" t="inlineStr">
+      <c r="D64" s="13" t="inlineStr">
         <is>
           <t>팔납동의 주인 · 맹수를 부리는 남만왕</t>
         </is>
       </c>
-      <c r="E64" s="12" t="inlineStr">
+      <c r="E64" s="13" t="inlineStr">
         <is>
           <t>76/58/70/28/44</t>
         </is>
       </c>
-      <c r="F64" s="12" t="inlineStr"/>
-      <c r="G64" s="12" t="inlineStr"/>
+      <c r="F64" s="13" t="inlineStr"/>
+      <c r="G64" s="13" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="12" t="n">
+      <c r="A65" s="13" t="n">
         <v>62</v>
       </c>
-      <c r="B65" s="12" t="inlineStr">
+      <c r="B65" s="13" t="inlineStr">
         <is>
           <t>전종</t>
         </is>
       </c>
-      <c r="C65" s="12" t="inlineStr">
+      <c r="C65" s="13" t="inlineStr">
         <is>
           <t>전종</t>
         </is>
       </c>
-      <c r="D65" s="12" t="inlineStr">
+      <c r="D65" s="13" t="inlineStr">
         <is>
           <t>오의 수군 대장</t>
         </is>
       </c>
-      <c r="E65" s="12" t="inlineStr">
+      <c r="E65" s="13" t="inlineStr">
         <is>
           <t>74/68/78/62/66</t>
         </is>
       </c>
-      <c r="F65" s="12" t="inlineStr"/>
-      <c r="G65" s="12" t="inlineStr"/>
+      <c r="F65" s="13" t="inlineStr"/>
+      <c r="G65" s="13" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="12" t="n">
+      <c r="A66" s="13" t="n">
         <v>63</v>
       </c>
-      <c r="B66" s="12" t="inlineStr">
+      <c r="B66" s="13" t="inlineStr">
         <is>
           <t>조우</t>
         </is>
       </c>
-      <c r="C66" s="12" t="inlineStr">
+      <c r="C66" s="13" t="inlineStr">
         <is>
           <t>조우</t>
         </is>
       </c>
-      <c r="D66" s="12" t="inlineStr">
+      <c r="D66" s="13" t="inlineStr">
         <is>
           <t>연왕 · 조예의 숙부</t>
         </is>
       </c>
-      <c r="E66" s="12" t="inlineStr">
+      <c r="E66" s="13" t="inlineStr">
         <is>
           <t>46/64/56/70/70</t>
         </is>
       </c>
-      <c r="F66" s="12" t="inlineStr"/>
-      <c r="G66" s="12" t="inlineStr"/>
+      <c r="F66" s="13" t="inlineStr"/>
+      <c r="G66" s="13" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="12" t="n">
+      <c r="A67" s="13" t="n">
         <v>64</v>
       </c>
-      <c r="B67" s="12" t="inlineStr">
+      <c r="B67" s="13" t="inlineStr">
         <is>
           <t>원희</t>
         </is>
       </c>
-      <c r="C67" s="12" t="inlineStr">
+      <c r="C67" s="13" t="inlineStr">
         <is>
           <t>원희</t>
         </is>
       </c>
-      <c r="D67" s="12" t="inlineStr">
+      <c r="D67" s="13" t="inlineStr">
         <is>
           <t>원소의 둘째 아들</t>
         </is>
       </c>
-      <c r="E67" s="12" t="inlineStr">
+      <c r="E67" s="13" t="inlineStr">
         <is>
           <t>64/52/62/48/58</t>
         </is>
       </c>
-      <c r="F67" s="12" t="inlineStr"/>
-      <c r="G67" s="12" t="inlineStr"/>
+      <c r="F67" s="13" t="inlineStr"/>
+      <c r="G67" s="13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/장수/이름있는_장수_목록.xlsx
+++ b/장수/이름있는_장수_목록.xlsx
@@ -2832,7 +2832,7 @@
       </c>
       <c r="O32" s="10" t="inlineStr">
         <is>
-          <t>물리 피해 15% 증가, 회심 확률 +15%p. 대신 받는 책략 피해 10% 증가.</t>
+          <t>매 공격(반격 포함)을 2회 연속으로 친다. 회심 확률 +10%p. 대신 받는 책략 피해 10% 증가.</t>
         </is>
       </c>
     </row>

--- a/장수/이름있는_장수_목록.xlsx
+++ b/장수/이름있는_장수_목록.xlsx
@@ -2832,7 +2832,7 @@
       </c>
       <c r="O32" s="10" t="inlineStr">
         <is>
-          <t>매 공격(반격 포함)을 2회 연속으로 친다. 회심 확률 +10%p. 대신 받는 책략 피해 10% 증가.</t>
+          <t>매 공격(반격 포함)을 2회 연속으로 친다. 회심 확률 +10%p. 대신 책략에 약해 받는 책략 피해 30% 증가.</t>
         </is>
       </c>
     </row>

--- a/장수/이름있는_장수_목록.xlsx
+++ b/장수/이름있는_장수_목록.xlsx
@@ -12,7 +12,7 @@
     <sheet name="병종으로 처리" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'이름있는 장수'!$A$4:$O$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'이름있는 장수'!$A$4:$P$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -599,7 +599,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>고유특성을 구현한 장수(규칙판 8)</t>
+          <t>고유특성을 구현한 장수(규칙판 8, 셋씩)</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
@@ -668,7 +668,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>· 노란 칸: 처음 제안한 초안. 초록 칸(구현된 고유특성): 실제 게임에 들어간 이름·효과(규칙판 8). 게임 엔진에 맞게 초안과 다르게 바꾼 것이 있다.</t>
+          <t>· 노란 칸: 처음 제안한 초안. 초록 칸(고유특성 1·2·3): 실제 게임에 들어간 이름·효과(규칙판 8). 첫째는 처음부터, 둘째는 병종 2단계(Lv.8 1차 진화), 셋째는 3단계(Lv.16 2차 진화)에서 열린다. 수치는 1단계 기준.</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:P99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -727,8 +727,9 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="52" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="60" customWidth="1" min="15" max="15"/>
+    <col width="44" customWidth="1" min="14" max="14"/>
+    <col width="44" customWidth="1" min="15" max="15"/>
+    <col width="44" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -813,12 +814,17 @@
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>구현된 고유특성(규칙판 8)</t>
+          <t>고유특성 1 (처음부터)</t>
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
-          <t>구현 효과(1단계 · 4단계는 ×1.5)</t>
+          <t>고유특성 2 (병종 2단계 · 1차 진화)</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>고유특성 3 (병종 3단계 · 2차 진화)</t>
         </is>
       </c>
     </row>
@@ -880,12 +886,17 @@
       </c>
       <c r="N5" s="10" t="inlineStr">
         <is>
-          <t>응시낭고</t>
+          <t>응시낭고 — 받는 책략 피해 25% 감소. 자기 차례마다 3칸 안 적 책사 하나의 책략을 봉인한다.</t>
         </is>
       </c>
       <c r="O5" s="10" t="inlineStr">
         <is>
-          <t>받는 책략 피해 25% 감소. 자기 차례마다 3칸 안 적 책사 하나의 책략을 봉인한다.</t>
+          <t>은인자중 — 받는 물리 피해 15% 감소, 체력 절반 이하에서는 25% 감소.</t>
+        </is>
+      </c>
+      <c r="P5" s="10" t="inlineStr">
+        <is>
+          <t>고평릉의 결단 — 체력이 절반 이하인 적에게 책략 피해 25% 증가.</t>
         </is>
       </c>
     </row>
@@ -947,12 +958,17 @@
       </c>
       <c r="N6" s="10" t="inlineStr">
         <is>
-          <t>난세의 간웅</t>
+          <t>난세의 간웅 — 이름있는 적 장수에게 주는 피해 20% 증가. 자기 차례마다 2칸 안 아군의 사기를 북돋운다(공격 +12%).</t>
         </is>
       </c>
       <c r="O6" s="10" t="inlineStr">
         <is>
-          <t>이름있는 적 장수에게 주는 피해 20% 증가. 자기 차례마다 2칸 안 아군의 사기를 북돋운다(공격 +12%).</t>
+          <t>위무지략 — 2칸 안 아군이 받는 피해 8% 감소.</t>
+        </is>
+      </c>
+      <c r="P6" s="10" t="inlineStr">
+        <is>
+          <t>치세의 능신 — 자기 차례마다 전장의 아군 모두 MP 2 회복.</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1036,17 @@
       </c>
       <c r="N7" s="10" t="inlineStr">
         <is>
-          <t>나의 결투</t>
+          <t>나의 결투 — 체력 절반 이하에서 물리 피해 30% 증가. 대신 받는 물리 피해 10% 증가.</t>
         </is>
       </c>
       <c r="O7" s="10" t="inlineStr">
         <is>
-          <t>체력 절반 이하에서 물리 피해 30% 증가. 대신 받는 물리 피해 10% 증가.</t>
+          <t>호위의 맹세 — 곁에 붙은 아군의 피해를 대신 받는다(관통 공격 제외). 받는 피해 5% 감소.</t>
+        </is>
+      </c>
+      <c r="P7" s="10" t="inlineStr">
+        <is>
+          <t>호치 — 물리 공격 회심 확률 +15%p.</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1114,17 @@
       </c>
       <c r="N8" s="10" t="inlineStr">
         <is>
-          <t>발시담정</t>
+          <t>발시담정 — 체력이 30% 이하로 떨어지면 자기 차례에 최대 체력의 25%를 회복한다(전투당 한 번).</t>
         </is>
       </c>
       <c r="O8" s="10" t="inlineStr">
         <is>
-          <t>체력이 30% 이하로 떨어지면 자기 차례에 최대 체력의 25%를 회복한다(전투당 한 번).</t>
+          <t>외눈의 노기 — 체력 절반 이하에서 물리 피해 20% 증가.</t>
+        </is>
+      </c>
+      <c r="P8" s="10" t="inlineStr">
+        <is>
+          <t>복양의 분전 — 받는 물리 피해 12% 감소.</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1186,17 @@
       </c>
       <c r="N9" s="10" t="inlineStr">
         <is>
-          <t>전이병귀신속</t>
+          <t>전이병귀신속 — 이번 차례 움직인 칸마다 물리 피해 4% 증가(최대 6칸).</t>
         </is>
       </c>
       <c r="O9" s="10" t="inlineStr">
         <is>
-          <t>이번 차례 움직인 칸마다 물리 피해 4% 증가(최대 6칸).</t>
+          <t>질풍 — 전투 첫 턴에 이동력 +3.</t>
+        </is>
+      </c>
+      <c r="P9" s="10" t="inlineStr">
+        <is>
+          <t>정군산의 급습 — 체력이 가득한 적에게 회심 확률 +20%p.</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1264,17 @@
       </c>
       <c r="N10" s="10" t="inlineStr">
         <is>
-          <t>요래요래</t>
+          <t>요래요래 — 체력이 가득한 적을 치면 피해 15% 증가, 반격을 받지 않는다.</t>
         </is>
       </c>
       <c r="O10" s="10" t="inlineStr">
         <is>
-          <t>체력이 가득한 적을 치면 피해 15% 증가, 반격을 받지 않는다.</t>
+          <t>합비의 귀신 — 곁에 붙은 적이 둘 이상이면 주는 피해 20% 증가.</t>
+        </is>
+      </c>
+      <c r="P10" s="10" t="inlineStr">
+        <is>
+          <t>소요진의 돌격 — 이름있는 적 장수를 치면 방어 25% 무시.</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1342,17 @@
       </c>
       <c r="N11" s="10" t="inlineStr">
         <is>
-          <t>장구한 포위</t>
+          <t>장구한 포위 — 대상 곁에 다른 아군이 둘 이상 붙어 있으면 피해 25% 증가.</t>
         </is>
       </c>
       <c r="O11" s="10" t="inlineStr">
         <is>
-          <t>대상 곁에 다른 아군이 둘 이상 붙어 있으면 피해 25% 증가.</t>
+          <t>도끼의 위엄 — 물리 공격이 방어 20% 무시.</t>
+        </is>
+      </c>
+      <c r="P11" s="10" t="inlineStr">
+        <is>
+          <t>번성 구원 — 2칸 안에서 체력이 절반 이하인 아군이 받는 피해 15% 감소.</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1420,17 @@
       </c>
       <c r="N12" s="10" t="inlineStr">
         <is>
-          <t>교변</t>
+          <t>교변 — 험한 지형도 평지처럼 움직인다. 두 칸 이상 떨어진 적에게 받는 피해 20% 감소.</t>
         </is>
       </c>
       <c r="O12" s="10" t="inlineStr">
         <is>
-          <t>험한 지형도 평지처럼 움직인다. 두 칸 이상 떨어진 적에게 받는 피해 20% 감소.</t>
+          <t>가정의 승리 — 산지·구릉에서 받는 피해 20% 감소.</t>
+        </is>
+      </c>
+      <c r="P12" s="10" t="inlineStr">
+        <is>
+          <t>목문도의 최후 — 체력 30% 이하에서 주는 피해 30% 증가.</t>
         </is>
       </c>
     </row>
@@ -1452,12 +1498,17 @@
       </c>
       <c r="N13" s="10" t="inlineStr">
         <is>
-          <t>철벽 수성</t>
+          <t>철벽 수성 — 성채·성문 칸에서 받는 피해 30% 감소, 그 밖에서는 8% 감소.</t>
         </is>
       </c>
       <c r="O13" s="10" t="inlineStr">
         <is>
-          <t>성채·성문 칸에서 받는 피해 30% 감소, 그 밖에서는 8% 감소.</t>
+          <t>대장의 위엄 — 곁에 붙은 아군이 받는 물리 피해 10% 감소.</t>
+        </is>
+      </c>
+      <c r="P13" s="10" t="inlineStr">
+        <is>
+          <t>불퇴 — 체력 절반 이하에서 받는 피해 15% 감소.</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1576,17 @@
       </c>
       <c r="N14" s="10" t="inlineStr">
         <is>
-          <t>왕좌지재</t>
+          <t>왕좌지재 — 자기 차례마다 전장의 아군 책사 모두의 책략 기력(MP)을 4 채운다.</t>
         </is>
       </c>
       <c r="O14" s="10" t="inlineStr">
         <is>
-          <t>자기 차례마다 전장의 아군 책사 모두의 책략 기력(MP)을 4 채운다.</t>
+          <t>구현의 주장 — 자기 차례마다 3칸 안 아군 하나의 혼란·봉인을 풀어 준다.</t>
+        </is>
+      </c>
+      <c r="P14" s="10" t="inlineStr">
+        <is>
+          <t>왕좌의 덕 — 받는 책략 피해 20% 감소.</t>
         </is>
       </c>
     </row>
@@ -1598,12 +1654,17 @@
       </c>
       <c r="N15" s="10" t="inlineStr">
         <is>
-          <t>금마초</t>
+          <t>금마초 — 움직인 뒤 공격하면 피해 15% 증가. 조씨 장수에게는 15% 더.</t>
         </is>
       </c>
       <c r="O15" s="10" t="inlineStr">
         <is>
-          <t>움직인 뒤 공격하면 피해 15% 증가. 조씨 장수에게는 15% 더.</t>
+          <t>금마초의 위용 — 전투 첫 두 턴 동안 적의 명중 -15%p.</t>
+        </is>
+      </c>
+      <c r="P15" s="10" t="inlineStr">
+        <is>
+          <t>복수의 창 — 곁에 붙은 적 하나마다 회심 확률 +7%p(최대 3).</t>
         </is>
       </c>
     </row>
@@ -1671,12 +1732,17 @@
       </c>
       <c r="N16" s="10" t="inlineStr">
         <is>
-          <t>인덕</t>
+          <t>인덕 — 자기 차례마다 곁에 붙은 아군의 체력을 8% 회복한다.</t>
         </is>
       </c>
       <c r="O16" s="10" t="inlineStr">
         <is>
-          <t>자기 차례마다 곁에 붙은 아군의 체력을 8% 회복한다.</t>
+          <t>삼고초려 — 자기 차례마다 2칸 안 아군 책사의 MP 3 회복.</t>
+        </is>
+      </c>
+      <c r="P16" s="10" t="inlineStr">
+        <is>
+          <t>한중왕 — 받는 피해 8% 감소, 체력 절반 이하에서는 18% 감소.</t>
         </is>
       </c>
     </row>
@@ -1744,12 +1810,17 @@
       </c>
       <c r="N17" s="10" t="inlineStr">
         <is>
-          <t>무성</t>
+          <t>무성 — 이름있는 적 장수를 물리 공격하면 피해 20% 증가, 회심 확률 +10%p.</t>
         </is>
       </c>
       <c r="O17" s="10" t="inlineStr">
         <is>
-          <t>이름있는 적 장수를 물리 공격하면 피해 20% 증가, 회심 확률 +10%p.</t>
+          <t>오관참육장 — 움직인 뒤 물리 공격하면 방어 20% 무시.</t>
+        </is>
+      </c>
+      <c r="P17" s="10" t="inlineStr">
+        <is>
+          <t>수엄칠군 — 물 위나 물가의 적에게 물리 피해 25% 증가.</t>
         </is>
       </c>
     </row>
@@ -1817,12 +1888,17 @@
       </c>
       <c r="N18" s="10" t="inlineStr">
         <is>
-          <t>장판교의 일갈</t>
+          <t>장판교의 일갈 — 자기 차례마다 2칸 안 적 모두를 쇠약하게 한다(공격 15% 감소).</t>
         </is>
       </c>
       <c r="O18" s="10" t="inlineStr">
         <is>
-          <t>자기 차례마다 2칸 안 적 모두를 쇠약하게 한다(공격 15% 감소).</t>
+          <t>연인 장익덕 — 물리 피해 12% 증가. 대신 받는 책략 피해 10% 증가.</t>
+        </is>
+      </c>
+      <c r="P18" s="10" t="inlineStr">
+        <is>
+          <t>의석 와구 — 숲·산지에서 받는 피해 15% 감소.</t>
         </is>
       </c>
     </row>
@@ -1890,12 +1966,17 @@
       </c>
       <c r="N19" s="10" t="inlineStr">
         <is>
-          <t>와룡</t>
+          <t>와룡 — 불·바람 책략 피해 25% 증가. 받는 책략 피해 15% 감소.</t>
         </is>
       </c>
       <c r="O19" s="10" t="inlineStr">
         <is>
-          <t>불·바람 책략 피해 25% 증가. 받는 책략 피해 15% 감소.</t>
+          <t>팔진도 — 자기 차례마다 2칸 안 적 모두를 둔화시킨다(이동력 감소).</t>
+        </is>
+      </c>
+      <c r="P19" s="10" t="inlineStr">
+        <is>
+          <t>목우유마 — 자기 차례마다 전장의 아군 모두 체력 2%와 MP 2 회복.</t>
         </is>
       </c>
     </row>
@@ -1963,12 +2044,17 @@
       </c>
       <c r="N20" s="10" t="inlineStr">
         <is>
-          <t>단기필마</t>
+          <t>단기필마 — 곁에 붙은 적이 둘 이상이면 받는 피해 25% 감소, 주는 피해 10% 증가.</t>
         </is>
       </c>
       <c r="O20" s="10" t="inlineStr">
         <is>
-          <t>곁에 붙은 적이 둘 이상이면 받는 피해 25% 감소, 주는 피해 10% 증가.</t>
+          <t>상산 조자룡 — 회피 +15%p.</t>
+        </is>
+      </c>
+      <c r="P20" s="10" t="inlineStr">
+        <is>
+          <t>일신시담 — 물리 회심 확률 +12%p. 체력이 가득하면 방어 15% 무시.</t>
         </is>
       </c>
     </row>
@@ -2036,12 +2122,17 @@
       </c>
       <c r="N21" s="10" t="inlineStr">
         <is>
-          <t>노익장</t>
+          <t>노익장 — 두 칸 이상 떨어진 적에게 물리 피해 15% 증가. 체력이 가득하면 회심 확률 +15%p.</t>
         </is>
       </c>
       <c r="O21" s="10" t="inlineStr">
         <is>
-          <t>두 칸 이상 떨어진 적에게 물리 피해 15% 증가. 체력이 가득하면 회심 확률 +15%p.</t>
+          <t>백발백중 — 명중 +20%p.</t>
+        </is>
+      </c>
+      <c r="P21" s="10" t="inlineStr">
+        <is>
+          <t>정군산의 일격 — 이름있는 적 장수를 두 칸 이상 떨어져 치면 피해 25% 증가.</t>
         </is>
       </c>
     </row>
@@ -2109,12 +2200,17 @@
       </c>
       <c r="N22" s="10" t="inlineStr">
         <is>
-          <t>기린아</t>
+          <t>기린아 — 물리 공격에 지력의 15%만큼 피해를 더한다. 책략 명중 +10%p.</t>
         </is>
       </c>
       <c r="O22" s="10" t="inlineStr">
         <is>
-          <t>물리 공격에 지력의 15%만큼 피해를 더한다. 책략 명중 +10%p.</t>
+          <t>담대함 — 체력 절반 이하에서 회피 +20%p.</t>
+        </is>
+      </c>
+      <c r="P22" s="10" t="inlineStr">
+        <is>
+          <t>일계 — 물리·책략 피해 모두 10% 증가.</t>
         </is>
       </c>
     </row>
@@ -2182,12 +2278,17 @@
       </c>
       <c r="N23" s="10" t="inlineStr">
         <is>
-          <t>연환계</t>
+          <t>연환계 — 책략 대상 곁에 붙은 다른 적 하나마다 책략 피해 8% 증가(최대 4).</t>
         </is>
       </c>
       <c r="O23" s="10" t="inlineStr">
         <is>
-          <t>책략 대상 곁에 붙은 다른 적 하나마다 책략 피해 8% 증가(최대 4).</t>
+          <t>낙봉파 — 자신의 체력이 가득할 때 책략 명중 +20%p.</t>
+        </is>
+      </c>
+      <c r="P23" s="10" t="inlineStr">
+        <is>
+          <t>연환의 쇠사슬 — 둔화·이동 불가인 적에게 불 책략 피해 35% 증가.</t>
         </is>
       </c>
     </row>
@@ -2255,12 +2356,17 @@
       </c>
       <c r="N24" s="10" t="inlineStr">
         <is>
-          <t>적벽의 화공</t>
+          <t>적벽의 화공 — 불 책략 피해 20% 증가. 물 위나 물가의 적에게는 30% 더.</t>
         </is>
       </c>
       <c r="O24" s="10" t="inlineStr">
         <is>
-          <t>불 책략 피해 20% 증가. 물 위나 물가의 적에게는 30% 더.</t>
+          <t>수군 대도독 — 물 위나 물가에서 주는 피해 15% 증가.</t>
+        </is>
+      </c>
+      <c r="P24" s="10" t="inlineStr">
+        <is>
+          <t>삼강구의 불 — 체력이 절반 이하인 적에게 불 책략 피해 25% 증가.</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2434,17 @@
       </c>
       <c r="N25" s="10" t="inlineStr">
         <is>
-          <t>벽안자염</t>
+          <t>벽안자염 — 3칸 안 아군 하나마다 받는 피해 5% 감소(최대 4). 자기 차례마다 MP 3 회복.</t>
         </is>
       </c>
       <c r="O25" s="10" t="inlineStr">
         <is>
-          <t>3칸 안 아군 하나마다 받는 피해 5% 감소(최대 4). 자기 차례마다 MP 3 회복.</t>
+          <t>자수의 계 — 받는 책략 피해 10% 감소.</t>
+        </is>
+      </c>
+      <c r="P25" s="10" t="inlineStr">
+        <is>
+          <t>강동의 인재 — 자기 차례마다 3칸 안 아군 MP 2 회복.</t>
         </is>
       </c>
     </row>
@@ -2401,12 +2512,17 @@
       </c>
       <c r="N26" s="10" t="inlineStr">
         <is>
-          <t>이릉의 화공</t>
+          <t>이릉의 화공 — 숲·갈대늪 위의 적에게 불 책략 피해 40% 증가.</t>
         </is>
       </c>
       <c r="O26" s="10" t="inlineStr">
         <is>
-          <t>숲·갈대늪 위의 적에게 불 책략 피해 40% 증가.</t>
+          <t>백면서생 — 이름있는 적 장수에게 책략 피해 15% 증가.</t>
+        </is>
+      </c>
+      <c r="P26" s="10" t="inlineStr">
+        <is>
+          <t>석정의 매복 — 숲에서 받는 피해 20% 감소.</t>
         </is>
       </c>
     </row>
@@ -2474,12 +2590,17 @@
       </c>
       <c r="N27" s="10" t="inlineStr">
         <is>
-          <t>백의도강</t>
+          <t>백의도강 — 전투 첫 두 턴 동안 주는 피해 25% 증가, 방어 15% 무시.</t>
         </is>
       </c>
       <c r="O27" s="10" t="inlineStr">
         <is>
-          <t>전투 첫 두 턴 동안 주는 피해 25% 증가, 방어 15% 무시.</t>
+          <t>괄목상대 — 자기보다 레벨이 높은 적에게 책략 피해 15% 증가.</t>
+        </is>
+      </c>
+      <c r="P27" s="10" t="inlineStr">
+        <is>
+          <t>오하아몽 — 책략 명중 +12%p.</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2668,17 @@
       </c>
       <c r="N28" s="10" t="inlineStr">
         <is>
-          <t>백기겁영</t>
+          <t>백기겁영 — 곁에 붙은 적 하나마다 회피 +8%p, 주는 피해 6% 증가(최대 3).</t>
         </is>
       </c>
       <c r="O28" s="10" t="inlineStr">
         <is>
-          <t>곁에 붙은 적 하나마다 회피 +8%p, 주는 피해 6% 증가(최대 3).</t>
+          <t>금범적 — 물 위나 물가에서 회심 확률 +15%p.</t>
+        </is>
+      </c>
+      <c r="P28" s="10" t="inlineStr">
+        <is>
+          <t>백 기의 야습 — 전투 첫 두 턴 동안 이동력 +2.</t>
         </is>
       </c>
     </row>
@@ -2614,12 +2740,17 @@
       </c>
       <c r="N29" s="10" t="inlineStr">
         <is>
-          <t>손유 동맹</t>
+          <t>손유 동맹 — 전장의 우군(동맹 부대)이 주는 피해 15% 증가.</t>
         </is>
       </c>
       <c r="O29" s="10" t="inlineStr">
         <is>
-          <t>전장의 우군(동맹 부대)이 주는 피해 15% 증가.</t>
+          <t>대국의 안목 — 받는 책략 피해 15% 감소.</t>
+        </is>
+      </c>
+      <c r="P29" s="10" t="inlineStr">
+        <is>
+          <t>단도회 — 곁에 붙은 아군이 없으면 받는 피해 15% 감소.</t>
         </is>
       </c>
     </row>
@@ -2681,12 +2812,17 @@
       </c>
       <c r="N30" s="10" t="inlineStr">
         <is>
-          <t>고육계</t>
+          <t>고육계 — 자기 차례마다 체력 5%를 잃고, 그 차례 동안 사기가 오른다. 체력이 낮을수록 피해 증가(최대 30%).</t>
         </is>
       </c>
       <c r="O30" s="10" t="inlineStr">
         <is>
-          <t>자기 차례마다 체력 5%를 잃고, 그 차례 동안 사기가 오른다. 체력이 낮을수록 피해 증가(최대 30%).</t>
+          <t>노장의 쇠채찍 — 물리 공격이 방어 15% 무시.</t>
+        </is>
+      </c>
+      <c r="P30" s="10" t="inlineStr">
+        <is>
+          <t>화선 — 물 위나 물가의 적에게 물리 피해 20% 증가.</t>
         </is>
       </c>
     </row>
@@ -2754,12 +2890,17 @@
       </c>
       <c r="N31" s="10" t="inlineStr">
         <is>
-          <t>반골</t>
+          <t>반골 — 곁에 붙은 아군이 없으면 주는 피해 25% 증가.</t>
         </is>
       </c>
       <c r="O31" s="10" t="inlineStr">
         <is>
-          <t>곁에 붙은 아군이 없으면 주는 피해 25% 증가.</t>
+          <t>한중 태수 — 길·다리 위에서 주는 피해 15% 증가.</t>
+        </is>
+      </c>
+      <c r="P31" s="10" t="inlineStr">
+        <is>
+          <t>홀로 선 칼 — 곁에 붙은 적이 하나뿐이면 물리 피해 20% 증가.</t>
         </is>
       </c>
     </row>
@@ -2827,12 +2968,17 @@
       </c>
       <c r="N32" s="10" t="inlineStr">
         <is>
-          <t>인중여포</t>
+          <t>인중여포 — 매 공격(반격 포함)을 2회 연속으로 친다. 회심 확률 +10%p. 대신 책략에 약해 받는 책략 피해 30% 증가.</t>
         </is>
       </c>
       <c r="O32" s="10" t="inlineStr">
         <is>
-          <t>매 공격(반격 포함)을 2회 연속으로 친다. 회심 확률 +10%p. 대신 책략에 약해 받는 책략 피해 30% 증가.</t>
+          <t>적토마 — 전투 첫 세 턴 동안 이동력 +2.</t>
+        </is>
+      </c>
+      <c r="P32" s="10" t="inlineStr">
+        <is>
+          <t>방천화극 — 자신의 체력이 가득할 때 받는 물리 피해 20% 감소.</t>
         </is>
       </c>
     </row>
@@ -2900,12 +3046,17 @@
       </c>
       <c r="N33" s="10" t="inlineStr">
         <is>
-          <t>냉철한 간파</t>
+          <t>냉철한 간파 — 책략 회피 +20%p. 자기 차례마다 자신의 혼란·봉인을 푼다.</t>
         </is>
       </c>
       <c r="O33" s="10" t="inlineStr">
         <is>
-          <t>책략 회피 +20%p. 자기 차례마다 자신의 혼란·봉인을 푼다.</t>
+          <t>하비의 계책 — 2칸 안 아군이 받는 책략 피해 10% 감소.</t>
+        </is>
+      </c>
+      <c r="P33" s="10" t="inlineStr">
+        <is>
+          <t>충절의 최후 — 체력 30% 이하에서 책략 피해 25% 증가.</t>
         </is>
       </c>
     </row>
@@ -2973,12 +3124,17 @@
       </c>
       <c r="N34" s="10" t="inlineStr">
         <is>
-          <t>관인대도</t>
+          <t>관인대도 — 자기 차례마다 전장의 아군 모두의 체력을 3% 회복한다.</t>
         </is>
       </c>
       <c r="O34" s="10" t="inlineStr">
         <is>
-          <t>자기 차례마다 전장의 아군 모두의 체력을 3% 회복한다.</t>
+          <t>한 고조 — 이름있는 아군 장수가 2칸 안에 있으면 받는 피해 15% 감소.</t>
+        </is>
+      </c>
+      <c r="P34" s="10" t="inlineStr">
+        <is>
+          <t>대풍가 — 전장의 아군 하나마다 주는 피해 2% 증가(최대 16%).</t>
         </is>
       </c>
     </row>
@@ -3046,12 +3202,17 @@
       </c>
       <c r="N35" s="10" t="inlineStr">
         <is>
-          <t>역발산기개세</t>
+          <t>역발산기개세 — 물리 피해 20% 증가. 체력 30% 이하(사면초가)에서는 30% 더.</t>
         </is>
       </c>
       <c r="O35" s="10" t="inlineStr">
         <is>
-          <t>물리 피해 20% 증가. 체력 30% 이하(사면초가)에서는 30% 더.</t>
+          <t>파부침주 — 전투 첫 두 턴 동안 받는 피해 20% 감소.</t>
+        </is>
+      </c>
+      <c r="P35" s="10" t="inlineStr">
+        <is>
+          <t>사면초가 — 곁에 붙은 적 하나마다 받는 피해 6% 감소(최대 4).</t>
         </is>
       </c>
     </row>
@@ -3113,12 +3274,17 @@
       </c>
       <c r="N36" s="10" t="inlineStr">
         <is>
-          <t>칠보시</t>
+          <t>칠보시 — 책략을 쓰는 적에게 주는 피해 20% 증가.</t>
         </is>
       </c>
       <c r="O36" s="10" t="inlineStr">
         <is>
-          <t>책략을 쓰는 적에게 주는 피해 20% 증가.</t>
+          <t>위 문제 — 2칸 안 아군이 받는 책략 피해 8% 감소.</t>
+        </is>
+      </c>
+      <c r="P36" s="10" t="inlineStr">
+        <is>
+          <t>전론 — 책략 명중 +15%p.</t>
         </is>
       </c>
     </row>
@@ -3176,6 +3342,7 @@
         </is>
       </c>
       <c r="O37" s="8" t="inlineStr"/>
+      <c r="P37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
@@ -3241,12 +3408,17 @@
       </c>
       <c r="N38" s="10" t="inlineStr">
         <is>
-          <t>난무</t>
+          <t>난무 — 혼란·봉인·쇠약·둔화에 걸린 적에게 주는 피해 30% 증가.</t>
         </is>
       </c>
       <c r="O38" s="10" t="inlineStr">
         <is>
-          <t>혼란·봉인·쇠약·둔화에 걸린 적에게 주는 피해 30% 증가.</t>
+          <t>완성의 계략 — 체력이 가득한 적에게 책략 피해 20% 증가.</t>
+        </is>
+      </c>
+      <c r="P38" s="10" t="inlineStr">
+        <is>
+          <t>독사 — 책략이 상대의 정신력을 20% 무시한다.</t>
         </is>
       </c>
     </row>
@@ -3304,6 +3476,7 @@
         </is>
       </c>
       <c r="O39" s="8" t="inlineStr"/>
+      <c r="P39" s="8" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
@@ -3359,6 +3532,7 @@
         </is>
       </c>
       <c r="O40" s="8" t="inlineStr"/>
+      <c r="P40" s="8" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
@@ -3410,6 +3584,7 @@
         </is>
       </c>
       <c r="O41" s="8" t="inlineStr"/>
+      <c r="P41" s="8" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
@@ -3465,6 +3640,7 @@
         </is>
       </c>
       <c r="O42" s="8" t="inlineStr"/>
+      <c r="P42" s="8" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
@@ -3524,12 +3700,17 @@
       </c>
       <c r="N43" s="10" t="inlineStr">
         <is>
-          <t>엄정한 군율</t>
+          <t>엄정한 군율 — 자기 차례마다 자신과 2칸 안 아군의 혼란·쇠약·둔화를 풀어 준다. 받는 피해 5% 감소.</t>
         </is>
       </c>
       <c r="O43" s="10" t="inlineStr">
         <is>
-          <t>자기 차례마다 자신과 2칸 안 아군의 혼란·쇠약·둔화를 풀어 준다. 받는 피해 5% 감소.</t>
+          <t>엄정 행군 — 자기 차례마다 이동력 +1.</t>
+        </is>
+      </c>
+      <c r="P43" s="10" t="inlineStr">
+        <is>
+          <t>정예 조련 — 2칸 안 아군 보병·창병이 받는 물리 피해 10% 감소.</t>
         </is>
       </c>
     </row>
@@ -3591,12 +3772,17 @@
       </c>
       <c r="N44" s="10" t="inlineStr">
         <is>
-          <t>선봉</t>
+          <t>선봉 — 첫 턴에 이동력 +2. 자신의 체력이 가득할 때 물리 피해 20% 증가.</t>
         </is>
       </c>
       <c r="O44" s="10" t="inlineStr">
         <is>
-          <t>첫 턴에 이동력 +2. 자신의 체력이 가득할 때 물리 피해 20% 증가.</t>
+          <t>작은 거인 — 자기보다 최대 체력이 큰 적에게 주는 피해 15% 증가.</t>
+        </is>
+      </c>
+      <c r="P44" s="10" t="inlineStr">
+        <is>
+          <t>합비 수비 — 성채·성문 칸에서 주는 피해 20% 증가.</t>
         </is>
       </c>
     </row>
@@ -3654,6 +3840,7 @@
         </is>
       </c>
       <c r="O45" s="8" t="inlineStr"/>
+      <c r="P45" s="8" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
@@ -3719,12 +3906,17 @@
       </c>
       <c r="N46" s="10" t="inlineStr">
         <is>
-          <t>음평 기습</t>
+          <t>음평 기습 — 산지·구릉에 서서 공격하면 피해 25% 증가.</t>
         </is>
       </c>
       <c r="O46" s="10" t="inlineStr">
         <is>
-          <t>산지·구릉에 서서 공격하면 피해 25% 증가.</t>
+          <t>둔전 — 자기 차례마다 최대 체력의 5% 회복.</t>
+        </is>
+      </c>
+      <c r="P46" s="10" t="inlineStr">
+        <is>
+          <t>면죽 돌파 — 이번 차례 4칸 이상 움직였으면 방어 25% 무시.</t>
         </is>
       </c>
     </row>
@@ -3792,12 +3984,17 @@
       </c>
       <c r="N47" s="10" t="inlineStr">
         <is>
-          <t>사본론</t>
+          <t>사본론 — 상대보다 지력이 높으면 그 차이만큼 책략 피해 증가(최대 25%).</t>
         </is>
       </c>
       <c r="O47" s="10" t="inlineStr">
         <is>
-          <t>상대보다 지력이 높으면 그 차이만큼 책략 피해 증가(최대 25%).</t>
+          <t>촉 정벌 — 이름있는 적 장수에게 받는 피해 15% 감소.</t>
+        </is>
+      </c>
+      <c r="P47" s="10" t="inlineStr">
+        <is>
+          <t>야심 — 자신의 체력이 가득할 때 책략 피해 20% 증가.</t>
         </is>
       </c>
     </row>
@@ -3859,12 +4056,17 @@
       </c>
       <c r="N48" s="10" t="inlineStr">
         <is>
-          <t>옹주 수비</t>
+          <t>옹주 수비 — 기병에게 받는 피해 30% 감소.</t>
         </is>
       </c>
       <c r="O48" s="10" t="inlineStr">
         <is>
-          <t>기병에게 받는 피해 30% 감소.</t>
+          <t>서방 수비 — 궁병·노병 같은 원거리 부대에게 받는 피해 20% 감소.</t>
+        </is>
+      </c>
+      <c r="P48" s="10" t="inlineStr">
+        <is>
+          <t>강유 저지 — 이름있는 적 장수에게 주는 피해 15% 증가.</t>
         </is>
       </c>
     </row>
@@ -3932,12 +4134,17 @@
       </c>
       <c r="N49" s="10" t="inlineStr">
         <is>
-          <t>진창 수성</t>
+          <t>진창 수성 — 성채·성문 칸에서 받은 물리 피해의 25%를 공격자에게 되돌린다.</t>
         </is>
       </c>
       <c r="O49" s="10" t="inlineStr">
         <is>
-          <t>성채·성문 칸에서 받은 물리 피해의 25%를 공격자에게 되돌린다.</t>
+          <t>구원 없는 수성 — 곁에 붙은 아군이 없으면 받는 피해 20% 감소.</t>
+        </is>
+      </c>
+      <c r="P49" s="10" t="inlineStr">
+        <is>
+          <t>진창의 불화살 — 성채·성문 칸에서 두 칸 이상 떨어진 적에게 피해 25% 증가.</t>
         </is>
       </c>
     </row>
@@ -3999,12 +4206,17 @@
       </c>
       <c r="N50" s="10" t="inlineStr">
         <is>
-          <t>침착한 장자</t>
+          <t>침착한 장자 — 사마의가 2칸 안에 있으면 주는 피해 15% 증가, 받는 피해 15% 감소.</t>
         </is>
       </c>
       <c r="O50" s="10" t="inlineStr">
         <is>
-          <t>사마의가 2칸 안에 있으면 주는 피해 15% 증가, 받는 피해 15% 감소.</t>
+          <t>대장군 — 2칸 안 아군의 물리 피해 8% 증가.</t>
+        </is>
+      </c>
+      <c r="P50" s="10" t="inlineStr">
+        <is>
+          <t>눈을 잃어도 — 적의 공격이 회심으로 터지지 않는다.</t>
         </is>
       </c>
     </row>
@@ -4066,12 +4278,17 @@
       </c>
       <c r="N51" s="10" t="inlineStr">
         <is>
-          <t>사마소의 마음</t>
+          <t>사마소의 마음 — 체력이 절반 이하인 적에게 주는 피해 20% 증가.</t>
         </is>
       </c>
       <c r="O51" s="10" t="inlineStr">
         <is>
-          <t>체력이 절반 이하인 적에게 주는 피해 20% 증가.</t>
+          <t>진왕 — 자기 차례마다 3칸 안 아군 체력 4% 회복.</t>
+        </is>
+      </c>
+      <c r="P51" s="10" t="inlineStr">
+        <is>
+          <t>촉 평정 — 물리 공격 명중 +15%p.</t>
         </is>
       </c>
     </row>
@@ -4133,12 +4350,17 @@
       </c>
       <c r="N52" s="10" t="inlineStr">
         <is>
-          <t>종실의 대들보</t>
+          <t>종실의 대들보 — 2칸 안 아군 기병의 물리 피해 12% 증가.</t>
         </is>
       </c>
       <c r="O52" s="10" t="inlineStr">
         <is>
-          <t>2칸 안 아군 기병의 물리 피해 12% 증가.</t>
+          <t>서방 대도독 — 곁에 아군 기병이 있으면 받는 물리 피해 10% 감소.</t>
+        </is>
+      </c>
+      <c r="P52" s="10" t="inlineStr">
+        <is>
+          <t>종실의 위세 — 자기 차례마다 2칸 안 아군 기병 이동력 +1.</t>
         </is>
       </c>
     </row>
@@ -4200,12 +4422,17 @@
       </c>
       <c r="N53" s="10" t="inlineStr">
         <is>
-          <t>헌마</t>
+          <t>헌마 — 곁에 붙은 아군이 받는 피해 10% 감소.</t>
         </is>
       </c>
       <c r="O53" s="10" t="inlineStr">
         <is>
-          <t>곁에 붙은 아군이 받는 피해 10% 감소.</t>
+          <t>헌마의 은혜 — 조조가 2칸 안에 있으면 받는 피해 20% 감소.</t>
+        </is>
+      </c>
+      <c r="P53" s="10" t="inlineStr">
+        <is>
+          <t>종실의 장수 — 자신의 체력이 가득할 때 받는 피해 15% 감소.</t>
         </is>
       </c>
     </row>
@@ -4273,12 +4500,17 @@
       </c>
       <c r="N54" s="10" t="inlineStr">
         <is>
-          <t>황수아</t>
+          <t>황수아 — 회심 확률 +10%p. 기병을 치면 피해 15% 증가.</t>
         </is>
       </c>
       <c r="O54" s="10" t="inlineStr">
         <is>
-          <t>회심 확률 +10%p. 기병을 치면 피해 15% 증가.</t>
+          <t>오환 정벌 — 움직인 뒤 공격하면 방어 15% 무시.</t>
+        </is>
+      </c>
+      <c r="P54" s="10" t="inlineStr">
+        <is>
+          <t>누런 수염 — 곁에 붙은 적이 셋 이상이면 물리 피해 25% 증가.</t>
         </is>
       </c>
     </row>
@@ -4340,12 +4572,17 @@
       </c>
       <c r="N55" s="10" t="inlineStr">
         <is>
-          <t>강하 수비</t>
+          <t>강하 수비 — 물가(물 칸 위나 옆)에서 받는 피해 20% 감소.</t>
         </is>
       </c>
       <c r="O55" s="10" t="inlineStr">
         <is>
-          <t>물가(물 칸 위나 옆)에서 받는 피해 20% 감소.</t>
+          <t>강하의 수군 — 물 위나 물가의 적에게 주는 피해 20% 증가.</t>
+        </is>
+      </c>
+      <c r="P55" s="10" t="inlineStr">
+        <is>
+          <t>충절 — 체력 30% 이하에서 받는 피해 25% 감소.</t>
         </is>
       </c>
     </row>
@@ -4403,6 +4640,7 @@
         </is>
       </c>
       <c r="O56" s="8" t="inlineStr"/>
+      <c r="P56" s="8" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
@@ -4458,6 +4696,7 @@
         </is>
       </c>
       <c r="O57" s="8" t="inlineStr"/>
+      <c r="P57" s="8" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
@@ -4517,12 +4756,17 @@
       </c>
       <c r="N58" s="10" t="inlineStr">
         <is>
-          <t>가정의 고지</t>
+          <t>가정의 고지 — 산지·구릉에서 책략 피해 20% 증가. 평지에서 받는 피해 10% 증가.</t>
         </is>
       </c>
       <c r="O58" s="10" t="inlineStr">
         <is>
-          <t>산지·구릉에서 책략 피해 20% 증가. 평지에서 받는 피해 10% 증가.</t>
+          <t>남만 심공 — 혼란에 빠진 적에게 책략 명중 +25%p.</t>
+        </is>
+      </c>
+      <c r="P58" s="10" t="inlineStr">
+        <is>
+          <t>읍참마속 — 체력 30% 이하에서 책략 피해 30% 증가.</t>
         </is>
       </c>
     </row>
@@ -4584,12 +4828,17 @@
       </c>
       <c r="N59" s="10" t="inlineStr">
         <is>
-          <t>흥세 수비</t>
+          <t>흥세 수비 — 길·다리·잔도 위에서 받는 피해 25% 감소.</t>
         </is>
       </c>
       <c r="O59" s="10" t="inlineStr">
         <is>
-          <t>길·다리·잔도 위에서 받는 피해 25% 감소.</t>
+          <t>가정의 수비 — 산지·구릉에서 두 칸 이상 떨어진 적에게 피해 20% 증가.</t>
+        </is>
+      </c>
+      <c r="P59" s="10" t="inlineStr">
+        <is>
+          <t>무당비군 — 숲에서 주는 피해 15% 증가.</t>
         </is>
       </c>
     </row>
@@ -4647,12 +4896,17 @@
       </c>
       <c r="N60" s="10" t="inlineStr">
         <is>
-          <t>부자 동행</t>
+          <t>부자 동행 — 관우가 2칸 안에 있으면 주는 피해 15% 증가, 받는 피해 15% 감소.</t>
         </is>
       </c>
       <c r="O60" s="10" t="inlineStr">
         <is>
-          <t>관우가 2칸 안에 있으면 주는 피해 15% 증가, 받는 피해 15% 감소.</t>
+          <t>청룡의 그림자 — 회심 확률 +8%p, 관우가 2칸 안에 있으면 8%p 더.</t>
+        </is>
+      </c>
+      <c r="P60" s="10" t="inlineStr">
+        <is>
+          <t>장자의 무예 — 보병·창병에게 받는 피해 15% 감소.</t>
         </is>
       </c>
     </row>
@@ -4710,6 +4964,7 @@
         </is>
       </c>
       <c r="O61" s="8" t="inlineStr"/>
+      <c r="P61" s="8" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
@@ -4761,6 +5016,7 @@
         </is>
       </c>
       <c r="O62" s="8" t="inlineStr"/>
+      <c r="P62" s="8" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
@@ -4812,6 +5068,7 @@
         </is>
       </c>
       <c r="O63" s="8" t="inlineStr"/>
+      <c r="P63" s="8" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
@@ -4867,12 +5124,17 @@
       </c>
       <c r="N64" s="10" t="inlineStr">
         <is>
-          <t>위연 참살</t>
+          <t>위연 참살 — 자기보다 레벨이 높은 적에게 주는 피해 20% 증가.</t>
         </is>
       </c>
       <c r="O64" s="10" t="inlineStr">
         <is>
-          <t>자기보다 레벨이 높은 적에게 주는 피해 20% 증가.</t>
+          <t>서량의 기병 — 움직인 뒤 공격하면 명중 +15%p.</t>
+        </is>
+      </c>
+      <c r="P64" s="10" t="inlineStr">
+        <is>
+          <t>복병 — 전투 첫 턴에 주는 피해 30% 증가.</t>
         </is>
       </c>
     </row>
@@ -4936,12 +5198,17 @@
       </c>
       <c r="N65" s="10" t="inlineStr">
         <is>
-          <t>칠종칠금</t>
+          <t>칠종칠금 — 자기 차례마다 최대 체력의 8%를 회복한다.</t>
         </is>
       </c>
       <c r="O65" s="10" t="inlineStr">
         <is>
-          <t>자기 차례마다 최대 체력의 8%를 회복한다.</t>
+          <t>등갑 동맹 — 받는 물리 피해 20% 감소. 대신 불 책략에 받는 피해 20% 증가.</t>
+        </is>
+      </c>
+      <c r="P65" s="10" t="inlineStr">
+        <is>
+          <t>일곱 번의 귀환 — 체력 30% 이하에서 주는 피해 25% 증가.</t>
         </is>
       </c>
     </row>
@@ -4999,12 +5266,17 @@
       </c>
       <c r="N66" s="10" t="inlineStr">
         <is>
-          <t>비도</t>
+          <t>비도 — 꼭 두 칸 떨어진 적에게 물리 피해 20% 증가, 명중 +15%p.</t>
         </is>
       </c>
       <c r="O66" s="10" t="inlineStr">
         <is>
-          <t>꼭 두 칸 떨어진 적에게 물리 피해 20% 증가, 명중 +15%p.</t>
+          <t>불의 신의 후예 — 불 책략에 받는 피해 30% 감소.</t>
+        </is>
+      </c>
+      <c r="P66" s="10" t="inlineStr">
+        <is>
+          <t>여장부 — 회피 +12%p.</t>
         </is>
       </c>
     </row>
@@ -5062,6 +5334,7 @@
         </is>
       </c>
       <c r="O67" s="8" t="inlineStr"/>
+      <c r="P67" s="8" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
@@ -5117,6 +5390,7 @@
         </is>
       </c>
       <c r="O68" s="8" t="inlineStr"/>
+      <c r="P68" s="8" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
@@ -5172,6 +5446,7 @@
         </is>
       </c>
       <c r="O69" s="8" t="inlineStr"/>
+      <c r="P69" s="8" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
@@ -5227,6 +5502,7 @@
         </is>
       </c>
       <c r="O70" s="8" t="inlineStr"/>
+      <c r="P70" s="8" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
@@ -5282,6 +5558,7 @@
         </is>
       </c>
       <c r="O71" s="8" t="inlineStr"/>
+      <c r="P71" s="8" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
@@ -5337,6 +5614,7 @@
         </is>
       </c>
       <c r="O72" s="8" t="inlineStr"/>
+      <c r="P72" s="8" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
@@ -5396,12 +5674,17 @@
       </c>
       <c r="N73" s="10" t="inlineStr">
         <is>
-          <t>의성</t>
+          <t>의성 — 전투 첫 세 턴 동안 받는 피해 25% 감소.</t>
         </is>
       </c>
       <c r="O73" s="10" t="inlineStr">
         <is>
-          <t>전투 첫 세 턴 동안 받는 피해 25% 감소.</t>
+          <t>강변 수비 — 물가에서 두 칸 이상 떨어진 적에게 피해 15% 증가.</t>
+        </is>
+      </c>
+      <c r="P73" s="10" t="inlineStr">
+        <is>
+          <t>동오의 견장 — 체력 절반 이하에서 받은 물리 피해의 15%를 되돌린다.</t>
         </is>
       </c>
     </row>
@@ -5463,12 +5746,17 @@
       </c>
       <c r="N74" s="10" t="inlineStr">
         <is>
-          <t>설중분전</t>
+          <t>설중분전 — 턴이 지날수록 주는 피해가 턴마다 3%씩 증가(최대 24%).</t>
         </is>
       </c>
       <c r="O74" s="10" t="inlineStr">
         <is>
-          <t>턴이 지날수록 주는 피해가 턴마다 3%씩 증가(최대 24%).</t>
+          <t>단병 돌격 — 물리 피해 20% 증가. 대신 받는 물리 피해 10% 증가.</t>
+        </is>
+      </c>
+      <c r="P74" s="10" t="inlineStr">
+        <is>
+          <t>노장의 기백 — 체력 절반 이하에서 회심 확률 +20%p.</t>
         </is>
       </c>
     </row>
@@ -5530,12 +5818,17 @@
       </c>
       <c r="N75" s="10" t="inlineStr">
         <is>
-          <t>형제의 외교</t>
+          <t>형제의 외교 — 자신과 곁에 붙은 아군이 받는 책략 피해 12% 감소.</t>
         </is>
       </c>
       <c r="O75" s="10" t="inlineStr">
         <is>
-          <t>자신과 곁에 붙은 아군이 받는 책략 피해 12% 감소.</t>
+          <t>온후한 장자 — 자기 차례마다 곁에 붙은 아군 체력 5% 회복.</t>
+        </is>
+      </c>
+      <c r="P75" s="10" t="inlineStr">
+        <is>
+          <t>외교 사절 — 책략을 쓰는 적에게 받는 피해 15% 감소.</t>
         </is>
       </c>
     </row>
@@ -5597,12 +5890,17 @@
       </c>
       <c r="N76" s="10" t="inlineStr">
         <is>
-          <t>강동 내정</t>
+          <t>강동 내정 — 2칸 안 아군의 책략 피해 10% 증가.</t>
         </is>
       </c>
       <c r="O76" s="10" t="inlineStr">
         <is>
-          <t>2칸 안 아군의 책략 피해 10% 증가.</t>
+          <t>직언 — 받는 책략 피해 15% 감소, 책략 명중 +5%p.</t>
+        </is>
+      </c>
+      <c r="P76" s="10" t="inlineStr">
+        <is>
+          <t>강동의 원로 — 2칸 안 아군의 책략 명중 +10%p.</t>
         </is>
       </c>
     </row>
@@ -5660,6 +5958,7 @@
         </is>
       </c>
       <c r="O77" s="8" t="inlineStr"/>
+      <c r="P77" s="8" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="n">
@@ -5721,12 +6020,17 @@
       </c>
       <c r="N78" s="10" t="inlineStr">
         <is>
-          <t>하북의 창</t>
+          <t>하북의 창 — 보병·창병을 치면 피해 25% 증가.</t>
         </is>
       </c>
       <c r="O78" s="10" t="inlineStr">
         <is>
-          <t>보병·창병을 치면 피해 25% 증가.</t>
+          <t>백마 포위 — 곁에 붙은 아군이 있으면 물리 피해 12% 증가.</t>
+        </is>
+      </c>
+      <c r="P78" s="10" t="inlineStr">
+        <is>
+          <t>백마의 선봉 — 전투 첫 턴에 회심 확률 +25%p.</t>
         </is>
       </c>
     </row>
@@ -5790,12 +6094,17 @@
       </c>
       <c r="N79" s="10" t="inlineStr">
         <is>
-          <t>하북의 칼</t>
+          <t>하북의 칼 — 궁병·노병 같은 원거리 부대를 치면 피해 25% 증가.</t>
         </is>
       </c>
       <c r="O79" s="10" t="inlineStr">
         <is>
-          <t>궁병·노병 같은 원거리 부대를 치면 피해 25% 증가.</t>
+          <t>연진의 추격 — 움직인 뒤 물리 공격하면 피해 12% 증가.</t>
+        </is>
+      </c>
+      <c r="P79" s="10" t="inlineStr">
+        <is>
+          <t>안량의 원수 — 체력 절반 이하에서 물리 피해 20% 증가, 명중 +10%p.</t>
         </is>
       </c>
     </row>
@@ -5853,6 +6162,7 @@
         </is>
       </c>
       <c r="O80" s="8" t="inlineStr"/>
+      <c r="P80" s="8" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
@@ -5904,6 +6214,7 @@
         </is>
       </c>
       <c r="O81" s="8" t="inlineStr"/>
+      <c r="P81" s="8" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
@@ -5959,6 +6270,7 @@
         </is>
       </c>
       <c r="O82" s="8" t="inlineStr"/>
+      <c r="P82" s="8" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="n">
@@ -6010,6 +6322,7 @@
         </is>
       </c>
       <c r="O83" s="8" t="inlineStr"/>
+      <c r="P83" s="8" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n">
@@ -6061,6 +6374,7 @@
         </is>
       </c>
       <c r="O84" s="8" t="inlineStr"/>
+      <c r="P84" s="8" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="n">
@@ -6116,6 +6430,7 @@
         </is>
       </c>
       <c r="O85" s="8" t="inlineStr"/>
+      <c r="P85" s="8" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="n">
@@ -6177,12 +6492,17 @@
       </c>
       <c r="N86" s="10" t="inlineStr">
         <is>
-          <t>감군</t>
+          <t>감군 — 2칸 안 아군의 명중 +10%p.</t>
         </is>
       </c>
       <c r="O86" s="10" t="inlineStr">
         <is>
-          <t>2칸 안 아군의 명중 +10%p.</t>
+          <t>감군의 진언 — 받는 책략 피해 12% 감소.</t>
+        </is>
+      </c>
+      <c r="P86" s="10" t="inlineStr">
+        <is>
+          <t>관도의 선견 — 전투 첫 두 턴 동안 2칸 안 아군이 받는 피해 10% 감소.</t>
         </is>
       </c>
     </row>
@@ -6250,12 +6570,17 @@
       </c>
       <c r="N87" s="10" t="inlineStr">
         <is>
-          <t>직간</t>
+          <t>직간 — 받은 책략 피해의 20%를 시전자에게 되돌린다.</t>
         </is>
       </c>
       <c r="O87" s="10" t="inlineStr">
         <is>
-          <t>받은 책략 피해의 20%를 시전자에게 되돌린다.</t>
+          <t>옥중의 충언 — 체력 절반 이하에서 책략 피해 20% 증가.</t>
+        </is>
+      </c>
+      <c r="P87" s="10" t="inlineStr">
+        <is>
+          <t>직언의 대가 — 받는 물리 피해 10% 감소.</t>
         </is>
       </c>
     </row>
@@ -6323,12 +6648,17 @@
       </c>
       <c r="N88" s="10" t="inlineStr">
         <is>
-          <t>업성 사수</t>
+          <t>업성 사수 — 체력이 많을수록 받는 피해 감소(가득하면 20%).</t>
         </is>
       </c>
       <c r="O88" s="10" t="inlineStr">
         <is>
-          <t>체력이 많을수록 받는 피해 감소(가득하면 20%).</t>
+          <t>업성의 결사 — 성채·성문 칸에서 주는 피해 15% 증가, 받는 피해 5% 감소.</t>
+        </is>
+      </c>
+      <c r="P88" s="10" t="inlineStr">
+        <is>
+          <t>충신의 기개 — 성채·성문 칸에 있으면 자기 차례마다 체력 8% 회복.</t>
         </is>
       </c>
     </row>
@@ -6386,6 +6716,7 @@
         </is>
       </c>
       <c r="O89" s="8" t="inlineStr"/>
+      <c r="P89" s="8" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
@@ -6447,12 +6778,17 @@
       </c>
       <c r="N90" s="10" t="inlineStr">
         <is>
-          <t>배수진</t>
+          <t>배수진 — 물을 등지고(물 칸 위나 옆) 싸우면 주는 피해 25% 증가.</t>
         </is>
       </c>
       <c r="O90" s="10" t="inlineStr">
         <is>
-          <t>물을 등지고(물 칸 위나 옆) 싸우면 주는 피해 25% 증가.</t>
+          <t>다다익선 — 2칸 안 아군 하나마다 주는 피해 5% 증가(최대 25%).</t>
+        </is>
+      </c>
+      <c r="P90" s="10" t="inlineStr">
+        <is>
+          <t>암도진창 — 전투 첫 턴에 이동력 +3, 둘째 턴에 +2.</t>
         </is>
       </c>
     </row>
@@ -6520,12 +6856,17 @@
       </c>
       <c r="N91" s="10" t="inlineStr">
         <is>
-          <t>운주유악</t>
+          <t>운주유악 — 2칸 안 아군의 회심 확률 +8%p.</t>
         </is>
       </c>
       <c r="O91" s="10" t="inlineStr">
         <is>
-          <t>2칸 안 아군의 회심 확률 +8%p.</t>
+          <t>황석공의 병법 — 책략 명중 +15%p, 받는 책략 피해 5% 감소.</t>
+        </is>
+      </c>
+      <c r="P91" s="10" t="inlineStr">
+        <is>
+          <t>초가의 노래 — 자기 차례마다 3칸 안에서 가장 가까운 적 하나를 쇠약하게 한다.</t>
         </is>
       </c>
     </row>
@@ -6589,12 +6930,17 @@
       </c>
       <c r="N92" s="10" t="inlineStr">
         <is>
-          <t>관중 경영</t>
+          <t>관중 경영 — 자기 차례마다 3칸 안에서 체력이 가장 낮은 아군 하나를 최대 체력의 12% 회복한다.</t>
         </is>
       </c>
       <c r="O92" s="10" t="inlineStr">
         <is>
-          <t>자기 차례마다 3칸 안에서 체력이 가장 낮은 아군 하나를 최대 체력의 12% 회복한다.</t>
+          <t>군량 보급 — 자기 차례마다 2칸 안 아군 MP 3 회복.</t>
+        </is>
+      </c>
+      <c r="P92" s="10" t="inlineStr">
+        <is>
+          <t>소규조수 — 받는 피해 10% 감소.</t>
         </is>
       </c>
     </row>
@@ -6658,12 +7004,17 @@
       </c>
       <c r="N93" s="10" t="inlineStr">
         <is>
-          <t>옥결</t>
+          <t>옥결 — 이름있는 적 장수에게 주는 책략 피해 25% 증가.</t>
         </is>
       </c>
       <c r="O93" s="10" t="inlineStr">
         <is>
-          <t>이름있는 적 장수에게 주는 책략 피해 25% 증가.</t>
+          <t>홍문의 계 — 체력이 가득한 적에게 책략 피해 15% 증가, 명중 +5%p.</t>
+        </is>
+      </c>
+      <c r="P93" s="10" t="inlineStr">
+        <is>
+          <t>아부 — 받는 책략 피해 18% 감소.</t>
         </is>
       </c>
     </row>
@@ -6727,12 +7078,17 @@
       </c>
       <c r="N94" s="10" t="inlineStr">
         <is>
-          <t>경형의 맹장</t>
+          <t>경형의 맹장 — 물리 공격으로 입힌 피해의 15%만큼 체력을 회복한다.</t>
         </is>
       </c>
       <c r="O94" s="10" t="inlineStr">
         <is>
-          <t>물리 공격으로 입힌 피해의 15%만큼 체력을 회복한다.</t>
+          <t>구강왕 — 곁에 붙은 적이 하나뿐이면 회심 확률 +15%p.</t>
+        </is>
+      </c>
+      <c r="P94" s="10" t="inlineStr">
+        <is>
+          <t>반골의 맹장 — 이름있는 적 장수에게 물리 피해 18% 증가.</t>
         </is>
       </c>
     </row>
@@ -6800,12 +7156,17 @@
       </c>
       <c r="N95" s="10" t="inlineStr">
         <is>
-          <t>유격</t>
+          <t>유격 — 숲·갈대늪 칸에서 회피 +20%p.</t>
         </is>
       </c>
       <c r="O95" s="10" t="inlineStr">
         <is>
-          <t>숲·갈대늪 칸에서 회피 +20%p.</t>
+          <t>유격의 귀재 — 이번 차례 움직였다면 받는 피해 12% 감소.</t>
+        </is>
+      </c>
+      <c r="P95" s="10" t="inlineStr">
+        <is>
+          <t>군량 차단 — 숲·갈대늪 칸에서 주는 피해 20% 증가.</t>
         </is>
       </c>
     </row>
@@ -6869,12 +7230,17 @@
       </c>
       <c r="N96" s="10" t="inlineStr">
         <is>
-          <t>홍문의 방패</t>
+          <t>홍문의 방패 — 곁에 붙은 아군의 피해를 대신 받는다(관통 공격 제외). 받는 물리 피해 10% 감소.</t>
         </is>
       </c>
       <c r="O96" s="10" t="inlineStr">
         <is>
-          <t>곁에 붙은 아군의 피해를 대신 받는다(관통 공격 제외). 받는 물리 피해 10% 감소.</t>
+          <t>돼지 다리 — 자기 차례마다 최대 체력의 6% 회복.</t>
+        </is>
+      </c>
+      <c r="P96" s="10" t="inlineStr">
+        <is>
+          <t>홍문의 일갈 — 자기 차례마다 곁에 붙은 적을 쇠약하게 한다.</t>
         </is>
       </c>
     </row>
@@ -6938,12 +7304,17 @@
       </c>
       <c r="N97" s="10" t="inlineStr">
         <is>
-          <t>반간계</t>
+          <t>반간계 — 세 턴마다 자기 차례에 3칸 안에서 지력이 가장 높은 적 하나를 혼란에 빠뜨린다.</t>
         </is>
       </c>
       <c r="O97" s="10" t="inlineStr">
         <is>
-          <t>세 턴마다 자기 차례에 3칸 안에서 지력이 가장 높은 적 하나를 혼란에 빠뜨린다.</t>
+          <t>육출기계 — 책략 피해 10% 증가, 받는 책략 피해 10% 감소.</t>
+        </is>
+      </c>
+      <c r="P97" s="10" t="inlineStr">
+        <is>
+          <t>반간의 대가 — 이름있는 적 장수에게 책략 명중 +20%p.</t>
         </is>
       </c>
     </row>
@@ -7001,12 +7372,17 @@
       </c>
       <c r="N98" s="10" t="inlineStr">
         <is>
-          <t>고군분투</t>
+          <t>고군분투 — 전장에 남은 아군이 셋 이하이면 주는 피해 20% 증가, 받는 피해 20% 감소.</t>
         </is>
       </c>
       <c r="O98" s="10" t="inlineStr">
         <is>
-          <t>전장에 남은 아군이 셋 이하이면 주는 피해 20% 증가, 받는 피해 20% 감소.</t>
+          <t>초의 골육 — 항우가 2칸 안에 있으면 받는 피해 15% 감소.</t>
+        </is>
+      </c>
+      <c r="P98" s="10" t="inlineStr">
+        <is>
+          <t>벗에게 몸을 맡기다 — 체력 30% 이하에서 회피 +25%p.</t>
         </is>
       </c>
     </row>
@@ -7070,17 +7446,22 @@
       </c>
       <c r="N99" s="10" t="inlineStr">
         <is>
-          <t>계포일낙</t>
+          <t>계포일낙 — 자기 차례마다 2칸 안에서 체력이 절반 이하인 아군을 견고하게 한다(받는 피해 감소).</t>
         </is>
       </c>
       <c r="O99" s="10" t="inlineStr">
         <is>
-          <t>자기 차례마다 2칸 안에서 체력이 절반 이하인 아군을 견고하게 한다(받는 피해 감소).</t>
+          <t>도망 장수의 지혜 — 이번 차례 움직였다면 회피 +15%p.</t>
+        </is>
+      </c>
+      <c r="P99" s="10" t="inlineStr">
+        <is>
+          <t>주가의 노비 — 받는 물리 피해 12% 감소, 체력 절반 이하면 반격 받은 피해 10% 되돌림.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:O99"/>
+  <autoFilter ref="A4:P99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/장수/이름있는_장수_목록.xlsx
+++ b/장수/이름있는_장수_목록.xlsx
@@ -668,7 +668,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>· 노란 칸: 처음 제안한 초안. 초록 칸(고유특성 1·2·3): 실제 게임에 들어간 이름·효과(규칙판 8). 첫째는 처음부터, 둘째는 병종 2단계(Lv.8 1차 진화), 셋째는 3단계(Lv.16 2차 진화)에서 열린다. 수치는 1단계 기준.</t>
+          <t>· 노란 칸: 처음 제안한 초안. 초록 칸(고유특성 1·2·3): 실제 게임에 들어간 이름·효과(규칙판 8). 첫째는 처음부터, 둘째는 2차 병종 진화(Lv.16~22), 셋째는 3차 병종 진화(Lv.30)에서 열린다. 수치는 1단계 기준.</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
-          <t>고유특성 2 (병종 2단계 · 1차 진화)</t>
+          <t>고유특성 2 (2차 병종 진화 · 병종 3단계)</t>
         </is>
       </c>
       <c r="P4" s="5" t="inlineStr">
         <is>
-          <t>고유특성 3 (병종 3단계 · 2차 진화)</t>
+          <t>고유특성 3 (3차 병종 진화 · 병종 4단계)</t>
         </is>
       </c>
     </row>
